--- a/cursor/product-pricing-analysis/Three_Mill_FOB_Landed.xlsx
+++ b/cursor/product-pricing-analysis/Three_Mill_FOB_Landed.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Three mills'!$A$1:$I$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Three mills'!$A$1:$I$231</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,10 +481,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -719,288 +719,296 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PEX-B PIPE — PEX-B PIPE</t>
+          <t>PEX-CPLNG — Coupling F2159 PPSU crimp</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="3" t="n">
-        <v>0.9838</v>
-      </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="5" t="n">
-        <v>1.0356</v>
-      </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="5" t="n">
-        <v>3.94</v>
-      </c>
+          <t>1"</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="4" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="4" t="n">
+        <v>0.6155</v>
+      </c>
+      <c r="I8" s="2" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PEX-B PIPE — PEX-B PIPE</t>
+          <t>PEX-CPLNG — Coupling F2159 PPSU crimp</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1-1/4"</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="3" t="n">
-        <v>0.6179</v>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="4" t="n">
-        <v>0.6504</v>
-      </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="5" t="n">
-        <v>2.47</v>
-      </c>
+          <t>1/2"</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.1024</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="4" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="4" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="I9" s="2" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PEX-B PIPE — PEX-B PIPE</t>
+          <t>PEX-CPLNG — Coupling F2159 PPSU crimp</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="6" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="5" t="n">
-        <v>2.0726</v>
-      </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="5" t="n">
-        <v>7.88</v>
-      </c>
+          <t>3/4"</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.1941</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="4" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="4" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="I10" s="2" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PEX-ELBOW — ELBOW</t>
+          <t>PEX-DE90 — Drop-ear / male elbow PEX x MPT F2159 PPSU</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="6" t="n">
-        <v>4.2433</v>
-      </c>
+          <t>1/2"</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="5" t="n">
-        <v>4.4667</v>
-      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
-      <c r="I11" s="5" t="n">
-        <v>16.97</v>
-      </c>
+      <c r="I11" s="2" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>PEX-ELBOW — ELBOW</t>
+          <t>PEX-DE90 — Drop-ear / male elbow PEX x MPT F2159 PPSU</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1-1/4"</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="6" t="n">
-        <v>2.4897</v>
-      </c>
+          <t>3/4"</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.6286</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="5" t="n">
-        <v>2.6207</v>
-      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.9048</v>
+      </c>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="5" t="n">
-        <v>9.960000000000001</v>
-      </c>
+      <c r="I12" s="2" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>PEX-ELBOW — ELBOW</t>
+          <t>PEX-ELBOW — 90 elbow F2159 PPSU crimp</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="6" t="n">
-        <v>8.5387</v>
-      </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="5" t="n">
-        <v>8.988099999999999</v>
-      </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="5" t="n">
-        <v>34.15</v>
-      </c>
+          <t>1"</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.5929</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="3" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.8597</v>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="4" t="n">
+        <v>0.8257</v>
+      </c>
+      <c r="I13" s="2" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDUCER — REDUCER</t>
+          <t>PEX-ELBOW — 90 elbow F2159 PPSU crimp</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1-1/2x3/4"</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="6" t="n">
-        <v>1.7339</v>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="5" t="n">
-        <v>1.8252</v>
-      </c>
-      <c r="H14" s="2" t="n"/>
+          <t>1/2"</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.4659</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.2149</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.4904</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.2437</v>
+      </c>
       <c r="I14" s="5" t="n">
-        <v>6.94</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDUCER — REDUCER</t>
+          <t>PEX-ELBOW — 90 elbow F2159 PPSU crimp</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2x3/4"</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="6" t="n">
-        <v>2.9513</v>
-      </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="5" t="n">
-        <v>3.1067</v>
-      </c>
-      <c r="H15" s="2" t="n"/>
+          <t>3/4"</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.7896</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.8310999999999999</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.4939</v>
+      </c>
       <c r="I15" s="5" t="n">
-        <v>11.81</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>PEX-CPLNG — Coupling F2159 PPSU crimp</t>
+          <t>PEX-FADPTR — Female swivel adapter PEX x FIPT F2159 PPSU</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
+          <t>1/2"</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.36</v>
+        <v>0.3143</v>
       </c>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="4" t="n">
-        <v>0.427</v>
-      </c>
+      <c r="E16" s="2" t="n"/>
       <c r="F16" s="4" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.4539</v>
       </c>
       <c r="G16" s="2" t="n"/>
-      <c r="H16" s="4" t="n">
-        <v>0.6155</v>
-      </c>
+      <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>PEX-CPLNG — Coupling F2159 PPSU crimp</t>
+          <t>PEX-FADPTR — Female swivel adapter PEX x FIPT F2159 PPSU</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
+          <t>3/4"</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.10235294117647</v>
+        <v>0.4857</v>
       </c>
       <c r="D17" s="2" t="n"/>
-      <c r="E17" s="4" t="n">
-        <v>0.104</v>
-      </c>
+      <c r="E17" s="2" t="n"/>
       <c r="F17" s="4" t="n">
-        <v>0.1481</v>
+        <v>0.7034</v>
       </c>
       <c r="G17" s="2" t="n"/>
-      <c r="H17" s="4" t="n">
-        <v>0.1536</v>
-      </c>
+      <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PEX-CPLNG — Coupling F2159 PPSU crimp</t>
+          <t>PEX-MADPTR — Male adapter PEX x MIPT F2159 PPSU</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
+          <t>1"</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.194117647058823</v>
+        <v>0.6</v>
       </c>
       <c r="D18" s="2" t="n"/>
-      <c r="E18" s="4" t="n">
-        <v>0.201</v>
-      </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="4" t="n">
-        <v>0.2811</v>
+        <v>0.8757</v>
       </c>
       <c r="G18" s="2" t="n"/>
-      <c r="H18" s="4" t="n">
-        <v>0.2923</v>
-      </c>
+      <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PEX-DE90 — Drop-ear / male elbow PEX x MPT F2159 PPSU</t>
+          <t>PEX-MADPTR — Male adapter PEX x MIPT F2159 PPSU</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1009,12 +1017,12 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.36</v>
+        <v>0.1941</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="4" t="n">
-        <v>0.5192</v>
+        <v>0.2805</v>
       </c>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
@@ -1023,7 +1031,7 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PEX-DE90 — Drop-ear / male elbow PEX x MPT F2159 PPSU</t>
+          <t>PEX-MADPTR — Male adapter PEX x MIPT F2159 PPSU</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1032,12 +1040,12 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.628571428571429</v>
+        <v>0.3106</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="4" t="n">
-        <v>0.9048</v>
+        <v>0.45</v>
       </c>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
@@ -1046,7 +1054,7 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PEX-ELBOW — 90 elbow F2159 PPSU crimp</t>
+          <t>PEX-PLUG — Plug F2159 PPSU</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1054,26 +1062,22 @@
           <t>1"</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
-        <v>0.592941176470588</v>
+      <c r="C21" s="3" t="n">
+        <v>0.2294</v>
       </c>
       <c r="D21" s="2" t="n"/>
-      <c r="E21" s="3" t="n">
-        <v>0.574</v>
-      </c>
+      <c r="E21" s="2" t="n"/>
       <c r="F21" s="4" t="n">
-        <v>0.8597</v>
+        <v>0.331</v>
       </c>
       <c r="G21" s="2" t="n"/>
-      <c r="H21" s="4" t="n">
-        <v>0.8257</v>
-      </c>
+      <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PEX-ELBOW — 90 elbow F2159 PPSU crimp</t>
+          <t>PEX-PLUG — Plug F2159 PPSU</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1082,31 +1086,21 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.148235294117647</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>0.4659</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0.167</v>
-      </c>
+        <v>0.06710000000000001</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
       <c r="F22" s="4" t="n">
-        <v>0.2149</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0.4904</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>0.2437</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>1.86</v>
-      </c>
+        <v>0.0968</v>
+      </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>PEX-ELBOW — 90 elbow F2159 PPSU crimp</t>
+          <t>PEX-PLUG — Plug F2159 PPSU</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1115,45 +1109,35 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.314117647058824</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>0.7896</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>0.342</v>
-      </c>
+        <v>0.1235</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
       <c r="F23" s="4" t="n">
-        <v>0.4551</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0.8310999999999999</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>0.4939</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>3.16</v>
-      </c>
+        <v>0.1784</v>
+      </c>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>PEX-FADPTR — Female swivel adapter PEX x FIPT F2159 PPSU</t>
+          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
+          <t>1" x 1" x 1/2"</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.314285714285714</v>
+        <v>0.5506</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="4" t="n">
-        <v>0.4539</v>
+        <v>0.7992</v>
       </c>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
@@ -1162,21 +1146,21 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>PEX-FADPTR — Female swivel adapter PEX x FIPT F2159 PPSU</t>
+          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
+          <t>1" x 1" x 3/4"</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.485714285714286</v>
+        <v>0.6353</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="4" t="n">
-        <v>0.7034</v>
+        <v>0.9262</v>
       </c>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
@@ -1185,21 +1169,21 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>PEX-MADPTR — Male adapter PEX x MIPT F2159 PPSU</t>
+          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
+          <t>1" x 3/4" x 1"</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.6</v>
+        <v>0.7059</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
-      <c r="F26" s="4" t="n">
-        <v>0.8757</v>
+      <c r="F26" s="5" t="n">
+        <v>1.0212</v>
       </c>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
@@ -1208,21 +1192,21 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>PEX-MADPTR — Male adapter PEX x MIPT F2159 PPSU</t>
+          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
+          <t>1" x 3/4" x 3/4"</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.194117647058823</v>
+        <v>0.5647</v>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="4" t="n">
-        <v>0.2805</v>
+        <v>0.8193</v>
       </c>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
@@ -1231,21 +1215,21 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>PEX-MADPTR — Male adapter PEX x MIPT F2159 PPSU</t>
+          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
+          <t>1/2" x 1/2" x 3/4"</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.310588235294118</v>
+        <v>0.2753</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="4" t="n">
-        <v>0.45</v>
+        <v>0.4025</v>
       </c>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
@@ -1254,21 +1238,21 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>PEX-PLUG — Plug F2159 PPSU</t>
+          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
+          <t>3/4" x 1/2" x 1/2"</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.229411764705882</v>
+        <v>0.3</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="4" t="n">
-        <v>0.331</v>
+        <v>0.4349</v>
       </c>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
@@ -1277,21 +1261,21 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PEX-PLUG — Plug F2159 PPSU</t>
+          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
+          <t>3/4" x 1/2" x 3/4"</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.0670588235294117</v>
+        <v>0.3706</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="4" t="n">
-        <v>0.0968</v>
+        <v>0.537</v>
       </c>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
@@ -1300,21 +1284,21 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PEX-PLUG — Plug F2159 PPSU</t>
+          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
+          <t>3/4" x 3/4" x 1"</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.123529411764706</v>
+        <v>0.5471</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="4" t="n">
-        <v>0.1784</v>
+        <v>0.8</v>
       </c>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
@@ -1328,62 +1312,72 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1" x 1" x 1/2"</t>
+          <t>3/4" x 3/4" x 1/2"</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.550588235294117</v>
+        <v>0.3529</v>
       </c>
       <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
+      <c r="E32" s="4" t="n">
+        <v>0.441</v>
+      </c>
       <c r="F32" s="4" t="n">
-        <v>0.7992</v>
+        <v>0.5118</v>
       </c>
       <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="H32" s="4" t="n">
+        <v>0.6355</v>
+      </c>
       <c r="I32" s="2" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
+          <t>PEX-REDUCER — Reducing coupling F2159 PPSU</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1" x 1" x 3/4"</t>
+          <t>1" x 1/2"</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.635294117647059</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
+        <v>0.2576</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0.7825</v>
+      </c>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="4" t="n">
-        <v>0.9262</v>
-      </c>
-      <c r="G33" s="2" t="n"/>
+        <v>0.3743</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0.8237</v>
+      </c>
       <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
+      <c r="I33" s="5" t="n">
+        <v>3.13</v>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
+          <t>PEX-REDUCER — Reducing coupling F2159 PPSU</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1" x 3/4" x 1"</t>
+          <t>1" x 3/4"</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.705882352941177</v>
+        <v>0.2894</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
-      <c r="F34" s="5" t="n">
-        <v>1.0212</v>
+      <c r="F34" s="4" t="n">
+        <v>0.4227</v>
       </c>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
@@ -1392,113 +1386,131 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
+          <t>PEX-REDUCER — Reducing coupling F2159 PPSU</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1" x 3/4" x 3/4"</t>
+          <t>3/4" x 1/2"</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.5647058823529409</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+        <v>0.1588</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0.501</v>
+      </c>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="4" t="n">
-        <v>0.8193</v>
-      </c>
-      <c r="G35" s="2" t="n"/>
+        <v>0.2307</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0.5274</v>
+      </c>
       <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
+      <c r="I35" s="5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
+          <t>PEX-TEE — Tee F2159 PPSU crimp</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1/2" x 1/2" x 3/4"</t>
+          <t>1"</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.275294117647059</v>
+        <v>0.8824</v>
       </c>
       <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="4" t="n">
-        <v>0.4025</v>
+      <c r="E36" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>1.2795</v>
       </c>
       <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
+      <c r="H36" s="5" t="n">
+        <v>1.3062</v>
+      </c>
       <c r="I36" s="2" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
+          <t>PEX-TEE — Tee F2159 PPSU crimp</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>3/4" x 1/2" x 1/2"</t>
+          <t>1/2"</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.3</v>
+        <v>0.2118</v>
       </c>
       <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
+      <c r="E37" s="4" t="n">
+        <v>0.23</v>
+      </c>
       <c r="F37" s="4" t="n">
-        <v>0.4349</v>
+        <v>0.3073</v>
       </c>
       <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="H37" s="4" t="n">
+        <v>0.3338</v>
+      </c>
       <c r="I37" s="2" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
+          <t>PEX-TEE — Tee F2159 PPSU crimp</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>3/4" x 1/2" x 3/4"</t>
+          <t>3/4"</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.370588235294118</v>
+        <v>0.4235</v>
       </c>
       <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
+      <c r="E38" s="4" t="n">
+        <v>0.474</v>
+      </c>
       <c r="F38" s="4" t="n">
-        <v>0.537</v>
+        <v>0.6145</v>
       </c>
       <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
+      <c r="H38" s="4" t="n">
+        <v>0.6827</v>
+      </c>
       <c r="I38" s="2" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
+          <t>PEX-F1807-CLAMP — Stainless steel pinch clamp</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>3/4" x 3/4" x 1"</t>
+          <t>1"</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.547058823529412</v>
+        <v>0.1327</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="n"/>
       <c r="F39" s="4" t="n">
-        <v>0.8</v>
+        <v>0.1933</v>
       </c>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
@@ -1507,77 +1519,67 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDTEE — Reducing tee F2159 PPSU</t>
+          <t>PEX-F1807-CLAMP — Stainless steel pinch clamp</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>3/4" x 3/4" x 1/2"</t>
+          <t>1/2"</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.352941176470588</v>
+        <v>0.0655</v>
       </c>
       <c r="D40" s="2" t="n"/>
-      <c r="E40" s="4" t="n">
-        <v>0.441</v>
-      </c>
+      <c r="E40" s="2" t="n"/>
       <c r="F40" s="4" t="n">
-        <v>0.5118</v>
+        <v>0.0945</v>
       </c>
       <c r="G40" s="2" t="n"/>
-      <c r="H40" s="4" t="n">
-        <v>0.6355</v>
-      </c>
+      <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDUCER — Reducing coupling F2159 PPSU</t>
+          <t>PEX-F1807-CLAMP — Stainless steel pinch clamp</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1" x 1/2"</t>
+          <t>3/4"</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.257647058823529</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>0.7825</v>
-      </c>
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="4" t="n">
-        <v>0.3743</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>0.8237</v>
-      </c>
+        <v>0.1359</v>
+      </c>
+      <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
-      <c r="I41" s="5" t="n">
-        <v>3.13</v>
-      </c>
+      <c r="I41" s="2" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDUCER — Reducing coupling F2159 PPSU</t>
+          <t>PEX-F1807-CPLNG — Coupling F1807 brass crimp</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1" x 3/4"</t>
+          <t>1"</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.289411764705882</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
-      <c r="F42" s="4" t="n">
-        <v>0.4227</v>
+      <c r="F42" s="5" t="n">
+        <v>1.3876</v>
       </c>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
@@ -1586,63 +1588,53 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>PEX-REDUCER — Reducing coupling F2159 PPSU</t>
+          <t>PEX-F1807-CPLNG — Coupling F1807 brass crimp</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>3/4" x 1/2"</t>
+          <t>1/2"</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.158823529411765</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>0.501</v>
-      </c>
+        <v>0.3593</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="4" t="n">
-        <v>0.2307</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0.5274</v>
-      </c>
+        <v>0.5163</v>
+      </c>
+      <c r="G43" s="2" t="n"/>
       <c r="H43" s="2" t="n"/>
-      <c r="I43" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="I43" s="2" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PEX-TEE — Tee F2159 PPSU crimp</t>
+          <t>PEX-F1807-CPLNG — Coupling F1807 brass crimp</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
+          <t>3/4"</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.882352941176471</v>
+        <v>0.5049</v>
       </c>
       <c r="D44" s="2" t="n"/>
-      <c r="E44" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>1.2795</v>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="4" t="n">
+        <v>0.7264</v>
       </c>
       <c r="G44" s="2" t="n"/>
-      <c r="H44" s="5" t="n">
-        <v>1.3062</v>
-      </c>
+      <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>PEX-TEE — Tee F2159 PPSU crimp</t>
+          <t>PEX-F1807-DE90 — Drop-ear 90 FPT F1807 brass</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1650,26 +1642,22 @@
           <t>1/2"</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>0.211764705882353</v>
+      <c r="C45" s="6" t="n">
+        <v>1.7965</v>
       </c>
       <c r="D45" s="2" t="n"/>
-      <c r="E45" s="4" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>0.3073</v>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="5" t="n">
+        <v>2.5779</v>
       </c>
       <c r="G45" s="2" t="n"/>
-      <c r="H45" s="4" t="n">
-        <v>0.3338</v>
-      </c>
+      <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>PEX-TEE — Tee F2159 PPSU crimp</t>
+          <t>PEX-F1807-DE90 — Drop-ear 90 FPT F1807 brass</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1677,26 +1665,22 @@
           <t>3/4"</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>0.423529411764706</v>
+      <c r="C46" s="6" t="n">
+        <v>1.999</v>
       </c>
       <c r="D46" s="2" t="n"/>
-      <c r="E46" s="4" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>0.6145</v>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="5" t="n">
+        <v>2.8763</v>
       </c>
       <c r="G46" s="2" t="n"/>
-      <c r="H46" s="4" t="n">
-        <v>0.6827</v>
-      </c>
+      <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-CLAMP — Stainless steel pinch clamp</t>
+          <t>PEX-F1807-ELBOW — 90 elbow F1807 brass crimp</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1704,13 +1688,13 @@
           <t>1"</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n">
-        <v>0.132684652808492</v>
+      <c r="C47" s="6" t="n">
+        <v>1.503</v>
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="n"/>
-      <c r="F47" s="4" t="n">
-        <v>0.1933</v>
+      <c r="F47" s="5" t="n">
+        <v>2.164</v>
       </c>
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
@@ -1719,7 +1703,7 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-CLAMP — Stainless steel pinch clamp</t>
+          <t>PEX-F1807-ELBOW — 90 elbow F1807 brass crimp</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1728,12 +1712,12 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.0654577620521893</v>
+        <v>0.4932</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="n"/>
       <c r="F48" s="4" t="n">
-        <v>0.0945</v>
+        <v>0.7077</v>
       </c>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
@@ -1742,7 +1726,7 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-CLAMP — Stainless steel pinch clamp</t>
+          <t>PEX-F1807-ELBOW — 90 elbow F1807 brass crimp</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1751,12 +1735,12 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.0937638213180009</v>
+        <v>0.775</v>
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="n"/>
-      <c r="F49" s="4" t="n">
-        <v>0.1359</v>
+      <c r="F49" s="5" t="n">
+        <v>1.1141</v>
       </c>
       <c r="G49" s="2" t="n"/>
       <c r="H49" s="2" t="n"/>
@@ -1765,7 +1749,7 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-CPLNG — Coupling F1807 brass crimp</t>
+          <t>PEX-F1807-FADPTR — PEX x FIPT adapter F1807 brass</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1773,13 +1757,13 @@
           <t>1"</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
-        <v>0.965177133655394</v>
+      <c r="C50" s="6" t="n">
+        <v>1.6908</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n"/>
       <c r="F50" s="5" t="n">
-        <v>1.3876</v>
+        <v>2.4326</v>
       </c>
       <c r="G50" s="2" t="n"/>
       <c r="H50" s="2" t="n"/>
@@ -1788,7 +1772,7 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-CPLNG — Coupling F1807 brass crimp</t>
+          <t>PEX-F1807-FADPTR — PEX x FIPT adapter F1807 brass</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1797,12 +1781,12 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.359299516908212</v>
+        <v>0.7397</v>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="n"/>
-      <c r="F51" s="4" t="n">
-        <v>0.5163</v>
+      <c r="F51" s="5" t="n">
+        <v>1.0637</v>
       </c>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
@@ -1811,7 +1795,7 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-CPLNG — Coupling F1807 brass crimp</t>
+          <t>PEX-F1807-FADPTR — PEX x FIPT adapter F1807 brass</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1819,13 +1803,13 @@
           <t>3/4"</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n">
-        <v>0.504898013955985</v>
+      <c r="C52" s="6" t="n">
+        <v>1.139</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n"/>
-      <c r="F52" s="4" t="n">
-        <v>0.7264</v>
+      <c r="F52" s="5" t="n">
+        <v>1.6376</v>
       </c>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
@@ -1834,21 +1818,21 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-DE90 — Drop-ear 90 FPT F1807 brass</t>
+          <t>PEX-F1807-MADPTR — PEX x MIPT adapter F1807 brass</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
+          <t>1"</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>1.79649758454106</v>
+        <v>1.6908</v>
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="5" t="n">
-        <v>2.5779</v>
+        <v>2.4326</v>
       </c>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
@@ -1857,21 +1841,21 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-DE90 — Drop-ear 90 FPT F1807 brass</t>
+          <t>PEX-F1807-MADPTR — PEX x MIPT adapter F1807 brass</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="n">
-        <v>1.999</v>
+          <t>1/2"</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0.7397</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="5" t="n">
-        <v>2.8763</v>
+        <v>1.0637</v>
       </c>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
@@ -1880,21 +1864,21 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-ELBOW — 90 elbow F1807 brass crimp</t>
+          <t>PEX-F1807-MADPTR — PEX x MIPT adapter F1807 brass</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
+          <t>3/4"</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>1.50295222758991</v>
+        <v>1.139</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="n"/>
       <c r="F55" s="5" t="n">
-        <v>2.164</v>
+        <v>1.6376</v>
       </c>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
@@ -1903,21 +1887,21 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-ELBOW — 90 elbow F1807 brass crimp</t>
+          <t>PEX-F1807-PLUG — Plug F1807 brass crimp</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
+          <t>1"</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.493156199677939</v>
+        <v>0.681</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n"/>
       <c r="F56" s="4" t="n">
-        <v>0.7077</v>
+        <v>0.9774</v>
       </c>
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
@@ -1926,21 +1910,21 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-ELBOW — 90 elbow F1807 brass crimp</t>
+          <t>PEX-F1807-PLUG — Plug F1807 brass crimp</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
+          <t>1/2"</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0.774959742351046</v>
+        <v>0.2701</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="n"/>
-      <c r="F57" s="5" t="n">
-        <v>1.1141</v>
+      <c r="F57" s="4" t="n">
+        <v>0.3877</v>
       </c>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
@@ -1949,21 +1933,21 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-FADPTR — PEX x FIPT adapter F1807 brass</t>
+          <t>PEX-F1807-PLUG — Plug F1807 brass crimp</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="n">
-        <v>1.69082125603865</v>
+          <t>3/4"</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0.3875</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
-      <c r="F58" s="5" t="n">
-        <v>2.4326</v>
+      <c r="F58" s="4" t="n">
+        <v>0.5566</v>
       </c>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
@@ -1972,21 +1956,21 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-FADPTR — PEX x FIPT adapter F1807 brass</t>
+          <t>PEX-F1807-REDCPL — Reducing coupling F1807 brass</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
+          <t>1" x 1/2"</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0.7397342995169079</v>
+        <v>0.732</v>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="n"/>
       <c r="F59" s="5" t="n">
-        <v>1.0637</v>
+        <v>1.0527</v>
       </c>
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="n"/>
@@ -1995,21 +1979,21 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-FADPTR — PEX x FIPT adapter F1807 brass</t>
+          <t>PEX-F1807-REDCPL — Reducing coupling F1807 brass</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="n">
-        <v>1.13895598497048</v>
+          <t>1" x 3/4"</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0.8102</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n"/>
       <c r="F60" s="5" t="n">
-        <v>1.6376</v>
+        <v>1.1645</v>
       </c>
       <c r="G60" s="2" t="n"/>
       <c r="H60" s="2" t="n"/>
@@ -2018,21 +2002,21 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-MADPTR — PEX x MIPT adapter F1807 brass</t>
+          <t>PEX-F1807-REDCPL — Reducing coupling F1807 brass</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>1.69082125603865</v>
+          <t>3/4" x 1/2"</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.4791</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="n"/>
-      <c r="F61" s="5" t="n">
-        <v>2.4326</v>
+      <c r="F61" s="4" t="n">
+        <v>0.6886</v>
       </c>
       <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="n"/>
@@ -2041,21 +2025,21 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-MADPTR — PEX x MIPT adapter F1807 brass</t>
+          <t>PEX-F1807-REDTEE — Reducing tee F1807 brass</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>0.7397342995169079</v>
+          <t>1" x 1" x 1/2"</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>1.3608</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n"/>
       <c r="F62" s="5" t="n">
-        <v>1.0637</v>
+        <v>1.9549</v>
       </c>
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="n"/>
@@ -2064,21 +2048,21 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-MADPTR — PEX x MIPT adapter F1807 brass</t>
+          <t>PEX-F1807-REDTEE — Reducing tee F1807 brass</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
+          <t>1" x 1" x 3/4"</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>1.13895598497048</v>
+        <v>1.5558</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="n"/>
       <c r="F63" s="5" t="n">
-        <v>1.6376</v>
+        <v>2.2365</v>
       </c>
       <c r="G63" s="2" t="n"/>
       <c r="H63" s="2" t="n"/>
@@ -2087,21 +2071,21 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-PLUG — Plug F1807 brass crimp</t>
+          <t>PEX-F1807-REDTEE — Reducing tee F1807 brass</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
+          <t>3/4" x 3/4" x 1/2"</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.681025228126677</v>
+        <v>0.9705</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="n"/>
-      <c r="F64" s="4" t="n">
-        <v>0.9774</v>
+      <c r="F64" s="5" t="n">
+        <v>1.3937</v>
       </c>
       <c r="G64" s="2" t="n"/>
       <c r="H64" s="2" t="n"/>
@@ -2110,21 +2094,21 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-PLUG — Plug F1807 brass crimp</t>
+          <t>PEX-F1807-RING — Copper crimp ring</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
+          <t>1"</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>0.270061728395062</v>
+        <v>0.2447</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" s="2" t="n"/>
       <c r="F65" s="4" t="n">
-        <v>0.3877</v>
+        <v>0.3535</v>
       </c>
       <c r="G65" s="2" t="n"/>
       <c r="H65" s="2" t="n"/>
@@ -2133,21 +2117,21 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-PLUG — Plug F1807 brass crimp</t>
+          <t>PEX-F1807-RING — Copper crimp ring</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
+          <t>1/2"</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.387479871175523</v>
+        <v>0.1385</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n"/>
       <c r="F66" s="4" t="n">
-        <v>0.5566</v>
+        <v>0.1989</v>
       </c>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
@@ -2156,21 +2140,21 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-REDCPL — Reducing coupling F1807 brass</t>
+          <t>PEX-F1807-RING — Copper crimp ring</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1" x 1/2"</t>
+          <t>3/4"</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0.732</v>
+        <v>0.1985</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" s="2" t="n"/>
-      <c r="F67" s="5" t="n">
-        <v>1.0527</v>
+      <c r="F67" s="4" t="n">
+        <v>0.2857</v>
       </c>
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="2" t="n"/>
@@ -2179,21 +2163,21 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-REDCPL — Reducing coupling F1807 brass</t>
+          <t>PEX-F1807-TEE — Tee F1807 brass crimp</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1" x 3/4"</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>0.810185185185185</v>
+          <t>1"</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>1.899</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
       <c r="F68" s="5" t="n">
-        <v>1.1645</v>
+        <v>2.7274</v>
       </c>
       <c r="G68" s="2" t="n"/>
       <c r="H68" s="2" t="n"/>
@@ -2202,21 +2186,21 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-REDCPL — Reducing coupling F1807 brass</t>
+          <t>PEX-F1807-TEE — Tee F1807 brass crimp</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>3/4" x 1/2"</t>
+          <t>1/2"</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>0.479066022544283</v>
+        <v>0.659</v>
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="n"/>
       <c r="F69" s="4" t="n">
-        <v>0.6886</v>
+        <v>0.9459</v>
       </c>
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
@@ -2225,21 +2209,21 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-REDTEE — Reducing tee F1807 brass</t>
+          <t>PEX-F1807-TEE — Tee F1807 brass crimp</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1" x 1" x 1/2"</t>
+          <t>3/4"</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>1.36084284460053</v>
+        <v>1.0544</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n"/>
       <c r="F70" s="5" t="n">
-        <v>1.9549</v>
+        <v>1.5148</v>
       </c>
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
@@ -2248,21 +2232,21 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-REDTEE — Reducing tee F1807 brass</t>
+          <t>PEX-F1807-VALVE — PEX x PEX ball valve F1807</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1" x 1" x 3/4"</t>
+          <t>1"</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>1.55575065847234</v>
+        <v>4.3732</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="n"/>
       <c r="F71" s="5" t="n">
-        <v>2.2365</v>
+        <v>6.2759</v>
       </c>
       <c r="G71" s="2" t="n"/>
       <c r="H71" s="2" t="n"/>
@@ -2271,21 +2255,21 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-REDTEE — Reducing tee F1807 brass</t>
+          <t>PEX-F1807-VALVE — PEX x PEX ball valve F1807</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>3/4" x 3/4" x 1/2"</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>0.970496894409938</v>
+          <t>1/2"</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>2.3843</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
       <c r="F72" s="5" t="n">
-        <v>1.3937</v>
+        <v>3.4273</v>
       </c>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
@@ -2294,21 +2278,21 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-RING — Copper crimp ring</t>
+          <t>PEX-F1807-VALVE — PEX x PEX ball valve F1807</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>0.244690674053555</v>
+          <t>3/4"</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>3.1032</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="n"/>
-      <c r="F73" s="4" t="n">
-        <v>0.3535</v>
+      <c r="F73" s="5" t="n">
+        <v>4.4553</v>
       </c>
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="n"/>
@@ -2317,7 +2301,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-RING — Copper crimp ring</t>
+          <t>PEX-ICEBOX — Ice maker outlet box 1/2 F1807</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2325,13 +2309,13 @@
           <t>1/2"</t>
         </is>
       </c>
-      <c r="C74" s="3" t="n">
-        <v>0.138504155124654</v>
+      <c r="C74" s="6" t="n">
+        <v>7.09</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n"/>
-      <c r="F74" s="4" t="n">
-        <v>0.1989</v>
+      <c r="F74" s="5" t="n">
+        <v>10.5818</v>
       </c>
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
@@ -2340,21 +2324,21 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-RING — Copper crimp ring</t>
+          <t>PEX-WMBOX — Washing machine outlet box 1/2 F1807, no WHA</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>0.198522622345337</v>
+          <t>1/2"</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>12.99</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" s="2" t="n"/>
-      <c r="F75" s="4" t="n">
-        <v>0.2857</v>
+      <c r="F75" s="5" t="n">
+        <v>19.0188</v>
       </c>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="n"/>
@@ -2363,21 +2347,21 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-TEE — Tee F1807 brass crimp</t>
+          <t>PEX-WMBOX-WHA — Washing machine outlet box 1/2 F1807 with water-hammer arrestors</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
+          <t>1/2"</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>1.899</v>
+        <v>20.99</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="n"/>
       <c r="F76" s="5" t="n">
-        <v>2.7274</v>
+        <v>30.4588</v>
       </c>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
@@ -2386,76 +2370,70 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-TEE — Tee F1807 brass crimp</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>0.658979372747489</v>
-      </c>
+          <t>1"</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n"/>
       <c r="E77" s="2" t="n"/>
-      <c r="F77" s="4" t="n">
-        <v>0.9459</v>
-      </c>
-      <c r="G77" s="2" t="n"/>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="4" t="n">
+        <v>0.7194</v>
+      </c>
       <c r="H77" s="2" t="n"/>
       <c r="I77" s="2" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-TEE — Tee F1807 brass crimp</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="n">
-        <v>1.05436699639598</v>
-      </c>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n"/>
       <c r="E78" s="2" t="n"/>
-      <c r="F78" s="5" t="n">
-        <v>1.5148</v>
-      </c>
-      <c r="G78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="5" t="n">
+        <v>1.1953</v>
+      </c>
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-VALVE — PEX x PEX ball valve F1807</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>1"</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="n">
-        <v>4.37322674641515</v>
-      </c>
+          <t>1-1/4"</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="n"/>
-      <c r="F79" s="5" t="n">
-        <v>6.2759</v>
-      </c>
-      <c r="G79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="4" t="n">
+        <v>0.9913999999999999</v>
+      </c>
       <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-VALVE — PEX x PEX ball valve F1807</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2463,214 +2441,192 @@
           <t>1/2"</t>
         </is>
       </c>
-      <c r="C80" s="6" t="n">
-        <v>2.38430718503182</v>
-      </c>
+      <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="n"/>
-      <c r="F80" s="5" t="n">
-        <v>3.4273</v>
-      </c>
-      <c r="G80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="4" t="n">
+        <v>0.3544</v>
+      </c>
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>PEX-F1807-VALVE — PEX x PEX ball valve F1807</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>3/4"</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="n">
-        <v>3.10319377348363</v>
-      </c>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="n"/>
-      <c r="F81" s="5" t="n">
-        <v>4.4553</v>
-      </c>
-      <c r="G81" s="2" t="n"/>
+      <c r="F81" s="2" t="n"/>
+      <c r="G81" s="5" t="n">
+        <v>1.6373</v>
+      </c>
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>PEX-ICEBOX — Ice maker outlet box 1/2 F1807</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="n">
-        <v>7.09</v>
-      </c>
+          <t>2-1/2"</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="n"/>
-      <c r="F82" s="5" t="n">
-        <v>10.5818</v>
-      </c>
-      <c r="G82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="5" t="n">
+        <v>2.5415</v>
+      </c>
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>PEX-WMBOX — Washing machine outlet box 1/2 F1807, no WHA</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="n">
-        <v>12.99</v>
-      </c>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n"/>
       <c r="E83" s="2" t="n"/>
-      <c r="F83" s="5" t="n">
-        <v>19.0188</v>
-      </c>
-      <c r="G83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="5" t="n">
+        <v>3.3552</v>
+      </c>
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="2" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>PEX-WMBOX-WHA — Washing machine outlet box 1/2 F1807 with water-hammer arrestors</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>1/2"</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="n">
-        <v>20.99</v>
-      </c>
+          <t>3/4"</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="n"/>
-      <c r="F84" s="5" t="n">
-        <v>30.4588</v>
-      </c>
-      <c r="G84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="4" t="n">
+        <v>0.4822</v>
+      </c>
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="2" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>PVC-PIPE-SOLID — ASTM D1785 Sch 40 PVC solid pipe (20 ft stick)</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="n">
-        <v>6.96063422583059</v>
-      </c>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n"/>
       <c r="E85" s="2" t="n"/>
-      <c r="F85" s="5" t="n">
-        <v>11.7262</v>
-      </c>
-      <c r="G85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="5" t="n">
+        <v>5.1712</v>
+      </c>
       <c r="H85" s="2" t="n"/>
-      <c r="I85" s="5" t="n">
-        <v>1.03</v>
-      </c>
+      <c r="I85" s="2" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>PVC-PIPE-SOLID — ASTM D1785 Sch 40 PVC solid pipe (20 ft stick)</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="n">
-        <v>9.35823155499209</v>
-      </c>
+          <t>5"</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="n"/>
-      <c r="F86" s="5" t="n">
-        <v>16.0411</v>
-      </c>
-      <c r="G86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="5" t="n">
+        <v>7.1369</v>
+      </c>
       <c r="H86" s="2" t="n"/>
-      <c r="I86" s="5" t="n">
-        <v>14.75</v>
-      </c>
+      <c r="I86" s="2" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>PVC-PIPE-SOLID — ASTM D1785 Sch 40 PVC solid pipe (20 ft stick)</t>
+          <t>PVC-PIPE-SCH80 — ASTM UPVC SCH80 PIPE</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="n">
-        <v>19.4290423741341</v>
-      </c>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="n"/>
-      <c r="F87" s="5" t="n">
-        <v>33.3965</v>
-      </c>
-      <c r="G87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="5" t="n">
+        <v>9.8171</v>
+      </c>
       <c r="H87" s="2" t="n"/>
-      <c r="I87" s="5" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="I87" s="2" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PVC-PIPE-SOLID — ASTM D1785 Sch 40 PVC solid pipe (20 ft stick)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="n">
-        <v>27.6570381124619</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+          <t>1"</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="3" t="n">
+        <v>0.1596</v>
+      </c>
       <c r="E88" s="2" t="n"/>
-      <c r="F88" s="5" t="n">
-        <v>49.1507</v>
-      </c>
-      <c r="G88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="4" t="n">
+        <v>0.551</v>
+      </c>
       <c r="H88" s="2" t="n"/>
-      <c r="I88" s="5" t="n">
-        <v>50</v>
+      <c r="I88" s="4" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>PVC-PIPE-FOAM — ASTM F891 PVC foam-core DWV pipe (20 ft stick)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 Sch 40 PVC solid pipe (20 ft stick)</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -2678,214 +2634,220 @@
           <t>1-1/2"</t>
         </is>
       </c>
-      <c r="C89" s="6" t="n">
-        <v>5.03730108448266</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="5" t="n">
+        <v>6.9606</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>5.1625</v>
+      </c>
       <c r="E89" s="2" t="n"/>
       <c r="F89" s="5" t="n">
-        <v>8.975899999999999</v>
-      </c>
-      <c r="G89" s="2" t="n"/>
+        <v>11.7262</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>17.817</v>
+      </c>
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="5" t="n">
-        <v>9.25</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>PVC-PIPE-FOAM — ASTM F891 PVC foam-core DWV pipe (20 ft stick)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="n">
-        <v>6.77240441479691</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+          <t>1-1/4"</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="3" t="n">
+        <v>0.2162</v>
+      </c>
       <c r="E90" s="2" t="n"/>
-      <c r="F90" s="5" t="n">
-        <v>12.3433</v>
-      </c>
-      <c r="G90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="4" t="n">
+        <v>0.7462</v>
+      </c>
       <c r="H90" s="2" t="n"/>
-      <c r="I90" s="5" t="n">
-        <v>11</v>
+      <c r="I90" s="4" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>PVC-PIPE-FOAM — ASTM F891 PVC foam-core DWV pipe (20 ft stick)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="n">
-        <v>14.0604911918076</v>
-      </c>
-      <c r="D91" s="2" t="n"/>
+          <t>1/2"</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="3" t="n">
+        <v>0.0809</v>
+      </c>
       <c r="E91" s="2" t="n"/>
-      <c r="F91" s="5" t="n">
-        <v>25.7195</v>
-      </c>
-      <c r="G91" s="2" t="n"/>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="4" t="n">
+        <v>0.2793</v>
+      </c>
       <c r="H91" s="2" t="n"/>
-      <c r="I91" s="5" t="n">
-        <v>19</v>
+      <c r="I91" s="4" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>PVC-PIPE-FOAM — ASTM F891 PVC foam-core DWV pipe (20 ft stick)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="n">
-        <v>20.0149617919133</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+          <t>10"</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="6" t="n">
+        <v>4.0306</v>
+      </c>
       <c r="E92" s="2" t="n"/>
-      <c r="F92" s="5" t="n">
-        <v>38.2226</v>
-      </c>
-      <c r="G92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="5" t="n">
+        <v>13.9105</v>
+      </c>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="5" t="n">
-        <v>27.6</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/16HH — 1/16 BEND (H x H)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
+          <t>12"</t>
         </is>
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n"/>
       <c r="E93" s="2" t="n"/>
       <c r="F93" s="2" t="n"/>
-      <c r="G93" s="4" t="n">
-        <v>0.162</v>
+      <c r="G93" s="5" t="n">
+        <v>18.3896</v>
       </c>
       <c r="H93" s="2" t="n"/>
-      <c r="I93" s="5" t="n">
-        <v>1.36</v>
-      </c>
+      <c r="I93" s="2" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/16HH — 1/16 BEND (H x H)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
+          <t>14"</t>
         </is>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="n"/>
       <c r="F94" s="2" t="n"/>
-      <c r="G94" s="4" t="n">
-        <v>0.2441</v>
+      <c r="G94" s="5" t="n">
+        <v>21.564</v>
       </c>
       <c r="H94" s="2" t="n"/>
-      <c r="I94" s="4" t="n">
-        <v>0.91</v>
-      </c>
+      <c r="I94" s="2" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/16HH — 1/16 BEND (H x H)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
+          <t>16"</t>
         </is>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n"/>
       <c r="E95" s="2" t="n"/>
       <c r="F95" s="2" t="n"/>
-      <c r="G95" s="4" t="n">
-        <v>0.8100000000000001</v>
+      <c r="G95" s="5" t="n">
+        <v>28.444</v>
       </c>
       <c r="H95" s="2" t="n"/>
-      <c r="I95" s="5" t="n">
-        <v>2.65</v>
-      </c>
+      <c r="I95" s="2" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/16HS — 1/16 BEND, STREET (H x S)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 Sch 40 PVC solid pipe (20 ft stick)</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n"/>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>9.3582</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>6.9407</v>
+      </c>
       <c r="E96" s="2" t="n"/>
-      <c r="F96" s="2" t="n"/>
-      <c r="G96" s="4" t="n">
-        <v>0.1519</v>
+      <c r="F96" s="5" t="n">
+        <v>16.0411</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>23.9541</v>
       </c>
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="5" t="n">
-        <v>2.05</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/16HS — 1/16 BEND, STREET (H x S)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
+          <t>2-1/2"</t>
         </is>
       </c>
       <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n"/>
+      <c r="D97" s="3" t="n">
+        <v>0.5508999999999999</v>
+      </c>
       <c r="E97" s="2" t="n"/>
       <c r="F97" s="2" t="n"/>
-      <c r="G97" s="4" t="n">
-        <v>0.2509</v>
+      <c r="G97" s="5" t="n">
+        <v>1.9014</v>
       </c>
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="5" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/16HS — 1/16 BEND, STREET (H x S)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 Sch 40 PVC solid pipe (20 ft stick)</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -2893,155 +2855,159 @@
           <t>3"</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="5" t="n">
+        <v>19.429</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>14.4099</v>
+      </c>
       <c r="E98" s="2" t="n"/>
-      <c r="F98" s="2" t="n"/>
-      <c r="G98" s="4" t="n">
-        <v>0.7538</v>
+      <c r="F98" s="5" t="n">
+        <v>33.3965</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>49.7323</v>
       </c>
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="5" t="n">
-        <v>7.46</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HH — 1/4 BEND (H x H)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
+          <t>3/4"</t>
         </is>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="3" t="n">
-        <v>0.2307</v>
+        <v>0.1075</v>
       </c>
       <c r="E99" s="2" t="n"/>
       <c r="F99" s="2" t="n"/>
       <c r="G99" s="4" t="n">
-        <v>0.2655</v>
+        <v>0.3709</v>
       </c>
       <c r="H99" s="2" t="n"/>
       <c r="I99" s="4" t="n">
-        <v>0.53</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HH — 1/4 BEND (H x H)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 Sch 40 PVC solid pipe (20 ft stick)</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="3" t="n">
-        <v>0.3734</v>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>27.657</v>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>20.5124</v>
       </c>
       <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="n"/>
-      <c r="G100" s="4" t="n">
-        <v>0.4298</v>
+      <c r="F100" s="5" t="n">
+        <v>49.1507</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>70.79340000000001</v>
       </c>
       <c r="H100" s="2" t="n"/>
-      <c r="I100" s="4" t="n">
-        <v>0.86</v>
+      <c r="I100" s="5" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HH — 1/4 BEND (H x H)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="n">
-        <v>1.1945566286216</v>
-      </c>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n"/>
       <c r="D101" s="6" t="n">
-        <v>1.1046</v>
+        <v>2.1731</v>
       </c>
       <c r="E101" s="2" t="n"/>
-      <c r="F101" s="5" t="n">
-        <v>2.4468</v>
-      </c>
+      <c r="F101" s="2" t="n"/>
       <c r="G101" s="5" t="n">
-        <v>1.2712</v>
+        <v>7.5</v>
       </c>
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="5" t="n">
-        <v>2.65</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HH — 1/4 BEND (H x H)</t>
+          <t>PVC-PIPE-SOLID — ASTM D1785 SCH40 PVC</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="n">
-        <v>2.35715539947322</v>
-      </c>
+          <t>8"</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n"/>
       <c r="D102" s="6" t="n">
-        <v>2.1055</v>
+        <v>2.8436</v>
       </c>
       <c r="E102" s="2" t="n"/>
-      <c r="F102" s="5" t="n">
-        <v>4.8478</v>
-      </c>
+      <c r="F102" s="2" t="n"/>
       <c r="G102" s="5" t="n">
-        <v>2.2163</v>
+        <v>9.8141</v>
       </c>
       <c r="H102" s="2" t="n"/>
       <c r="I102" s="5" t="n">
-        <v>4.99</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HH — 1/4 BEND (H × H)</t>
+          <t>PVC-PIPE-FOAM — ASTM F891 PVC foam-core DWV pipe (20 ft stick)</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>6"</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="6" t="n">
-        <v>5.7095</v>
-      </c>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>5.0373</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" s="2" t="n"/>
-      <c r="F103" s="2" t="n"/>
+      <c r="F103" s="5" t="n">
+        <v>8.975899999999999</v>
+      </c>
       <c r="G103" s="5" t="n">
-        <v>6.01</v>
+        <v>16.394</v>
       </c>
       <c r="H103" s="2" t="n"/>
       <c r="I103" s="5" t="n">
-        <v>22.84</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HHLNG — LONG SWEEP 1/4 BEND (H x H)</t>
+          <t>PVC-PIPE-FOAM — ASTM F891 PVC foam-core DWV pipe (20 ft stick)</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -3049,26 +3015,26 @@
           <t>2"</t>
         </is>
       </c>
-      <c r="C104" s="3" t="n">
-        <v>0.464442493415277</v>
+      <c r="C104" s="6" t="n">
+        <v>6.7724</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" s="2" t="n"/>
-      <c r="F104" s="4" t="n">
-        <v>0.7667</v>
-      </c>
-      <c r="G104" s="4" t="n">
-        <v>0.5153</v>
+      <c r="F104" s="5" t="n">
+        <v>12.3433</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>22.95</v>
       </c>
       <c r="H104" s="2" t="n"/>
       <c r="I104" s="5" t="n">
-        <v>1.34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HHLNG — LONG SWEEP 1/4 BEND (H x H)</t>
+          <t>PVC-PIPE-FOAM — ASTM F891 PVC foam-core DWV pipe (20 ft stick)</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -3077,25 +3043,25 @@
         </is>
       </c>
       <c r="C105" s="6" t="n">
-        <v>1.24635645302897</v>
+        <v>14.0605</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" s="2" t="n"/>
       <c r="F105" s="5" t="n">
-        <v>2.0285</v>
+        <v>25.7195</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1.485</v>
+        <v>39.344</v>
       </c>
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="5" t="n">
-        <v>3.17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HHLNG — LONG SWEEP 1/4 BEND (H x H)</t>
+          <t>PVC-PIPE-FOAM — ASTM F891 PVC foam-core DWV pipe (20 ft stick)</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -3104,25 +3070,25 @@
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>2.4451273046532</v>
+        <v>20.015</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" s="2" t="n"/>
       <c r="F106" s="5" t="n">
-        <v>4.0241</v>
+        <v>38.2226</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>2.5875</v>
+        <v>60.328</v>
       </c>
       <c r="H106" s="2" t="n"/>
       <c r="I106" s="5" t="n">
-        <v>6.47</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HS — 1/4 BEND, STREET (H x S)</t>
+          <t>PVC-1/16HH — 1/16 BEND (H x H)</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -3135,17 +3101,17 @@
       <c r="E107" s="2" t="n"/>
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="4" t="n">
-        <v>0.2295</v>
+        <v>0.162</v>
       </c>
       <c r="H107" s="2" t="n"/>
-      <c r="I107" s="4" t="n">
-        <v>0.7</v>
+      <c r="I107" s="5" t="n">
+        <v>1.36</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HS — 1/4 BEND, STREET (H x S)</t>
+          <t>PVC-1/16HH — 1/16 BEND (H x H)</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -3158,17 +3124,17 @@
       <c r="E108" s="2" t="n"/>
       <c r="F108" s="2" t="n"/>
       <c r="G108" s="4" t="n">
-        <v>0.3848</v>
+        <v>0.2441</v>
       </c>
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="4" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HS — 1/4 BEND, STREET (H x S)</t>
+          <t>PVC-1/16HH — 1/16 BEND (H x H)</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -3180,1417 +3146,1411 @@
       <c r="D109" s="2" t="n"/>
       <c r="E109" s="2" t="n"/>
       <c r="F109" s="2" t="n"/>
-      <c r="G109" s="5" t="n">
-        <v>1.215</v>
+      <c r="G109" s="4" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="5" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4HS — 1/4 BEND, STREET (H x S)</t>
+          <t>PVC-1/16HS — 1/16 BEND, STREET (H x S)</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
+          <t>1-1/2"</t>
         </is>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n"/>
       <c r="E110" s="2" t="n"/>
       <c r="F110" s="2" t="n"/>
-      <c r="G110" s="5" t="n">
-        <v>2.16</v>
+      <c r="G110" s="4" t="n">
+        <v>0.1519</v>
       </c>
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="5" t="n">
-        <v>4.86</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/4LOWHEEL — 1/4 BEND W/ LOW HEEL INLET (H x H x H)</t>
+          <t>PVC-1/16HS — 1/16 BEND, STREET (H x S)</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>3" x 3" x 2"</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="n">
-        <v>1.64934152765584</v>
-      </c>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n"/>
       <c r="E111" s="2" t="n"/>
-      <c r="F111" s="5" t="n">
-        <v>3.0971</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>1.3163</v>
+      <c r="F111" s="2" t="n"/>
+      <c r="G111" s="4" t="n">
+        <v>0.2509</v>
       </c>
       <c r="H111" s="2" t="n"/>
       <c r="I111" s="5" t="n">
-        <v>4.11</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/8HH — 1/8 BEND (H x H)</t>
+          <t>PVC-1/16HS — 1/16 BEND, STREET (H x S)</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>0.314661984196664</v>
-      </c>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n"/>
       <c r="E112" s="2" t="n"/>
-      <c r="F112" s="4" t="n">
-        <v>0.5091</v>
-      </c>
+      <c r="F112" s="2" t="n"/>
       <c r="G112" s="4" t="n">
-        <v>0.2273</v>
+        <v>0.7538</v>
       </c>
       <c r="H112" s="2" t="n"/>
-      <c r="I112" s="4" t="n">
-        <v>0.52</v>
+      <c r="I112" s="5" t="n">
+        <v>7.46</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/8HH — 1/8 BEND (H x H)</t>
+          <t>PVC-1/4HH — 1/4 BEND (H x H)</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="n">
-        <v>0.464442493415277</v>
-      </c>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n"/>
       <c r="D113" s="3" t="n">
-        <v>0.306</v>
+        <v>0.2307</v>
       </c>
       <c r="E113" s="2" t="n"/>
-      <c r="F113" s="4" t="n">
-        <v>0.7667</v>
-      </c>
+      <c r="F113" s="2" t="n"/>
       <c r="G113" s="4" t="n">
-        <v>0.3521</v>
+        <v>0.2655</v>
       </c>
       <c r="H113" s="2" t="n"/>
       <c r="I113" s="4" t="n">
-        <v>0.79</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/8HH — 1/8 BEND (H x H)</t>
+          <t>PVC-1/4HH — 1/4 BEND (H x H)</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="n">
-        <v>1.24635645302897</v>
-      </c>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n"/>
       <c r="D114" s="3" t="n">
-        <v>0.9091</v>
+        <v>0.3734</v>
       </c>
       <c r="E114" s="2" t="n"/>
-      <c r="F114" s="5" t="n">
-        <v>2.0285</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>1.0462</v>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="4" t="n">
+        <v>0.4298</v>
       </c>
       <c r="H114" s="2" t="n"/>
-      <c r="I114" s="5" t="n">
-        <v>2.16</v>
+      <c r="I114" s="4" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/8HH — 1/8 BEND (H x H)</t>
+          <t>PVC-1/4HH — 1/4 BEND (H x H)</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
+          <t>3"</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>2.4451273046532</v>
+        <v>1.1946</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>1.6227</v>
+        <v>1.1046</v>
       </c>
       <c r="E115" s="2" t="n"/>
       <c r="F115" s="5" t="n">
-        <v>4.0241</v>
+        <v>2.4468</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>1.8675</v>
+        <v>1.2712</v>
       </c>
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="5" t="n">
-        <v>4.11</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/8HH — 1/8 BEND (H × H)</t>
+          <t>PVC-1/4HH — 1/4 BEND (H x H)</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>6"</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n"/>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>2.3572</v>
+      </c>
       <c r="D116" s="6" t="n">
-        <v>3.5094</v>
+        <v>2.1055</v>
       </c>
       <c r="E116" s="2" t="n"/>
-      <c r="F116" s="2" t="n"/>
+      <c r="F116" s="5" t="n">
+        <v>4.8478</v>
+      </c>
       <c r="G116" s="5" t="n">
-        <v>3.6941</v>
+        <v>2.2163</v>
       </c>
       <c r="H116" s="2" t="n"/>
       <c r="I116" s="5" t="n">
-        <v>14.04</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/8HH — 1/8 BEND (H × H)</t>
+          <t>PVC-1/4HH — 1/4 BEND (H × H)</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>8"</t>
+          <t>6"</t>
         </is>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="6" t="n">
-        <v>6.7353</v>
+        <v>5.7095</v>
       </c>
       <c r="E117" s="2" t="n"/>
       <c r="F117" s="2" t="n"/>
       <c r="G117" s="5" t="n">
-        <v>7.0898</v>
+        <v>6.01</v>
       </c>
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="5" t="n">
-        <v>26.94</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/8HS — 1/8 BEND STREET (H x S)</t>
+          <t>PVC-1/4HHLNG — LONG SWEEP 1/4 BEND (H x H)</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n"/>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0.4644</v>
+      </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n"/>
+      <c r="F118" s="4" t="n">
+        <v>0.7667</v>
+      </c>
       <c r="G118" s="4" t="n">
-        <v>0.2273</v>
+        <v>0.5153</v>
       </c>
       <c r="H118" s="2" t="n"/>
-      <c r="I118" s="4" t="n">
-        <v>0.49</v>
+      <c r="I118" s="5" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/8HS — 1/8 BEND STREET (H x S)</t>
+          <t>PVC-1/4HHLNG — LONG SWEEP 1/4 BEND (H x H)</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n"/>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>1.2464</v>
+      </c>
       <c r="D119" s="2" t="n"/>
       <c r="E119" s="2" t="n"/>
-      <c r="F119" s="2" t="n"/>
-      <c r="G119" s="4" t="n">
-        <v>0.35</v>
+      <c r="F119" s="5" t="n">
+        <v>2.0285</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>1.485</v>
       </c>
       <c r="H119" s="2" t="n"/>
-      <c r="I119" s="4" t="n">
-        <v>0.82</v>
+      <c r="I119" s="5" t="n">
+        <v>3.17</v>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/8HS — 1/8 BEND STREET (H x S)</t>
+          <t>PVC-1/4HHLNG — LONG SWEEP 1/4 BEND (H x H)</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n"/>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="n">
+        <v>2.4451</v>
+      </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" s="2" t="n"/>
-      <c r="F120" s="2" t="n"/>
+      <c r="F120" s="5" t="n">
+        <v>4.0241</v>
+      </c>
       <c r="G120" s="5" t="n">
-        <v>1.0013</v>
+        <v>2.5875</v>
       </c>
       <c r="H120" s="2" t="n"/>
       <c r="I120" s="5" t="n">
-        <v>2.22</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>PVC-1/8HS — 1/8 BEND STREET (H x S)</t>
+          <t>PVC-1/4HS — 1/4 BEND, STREET (H x S)</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
+          <t>1-1/2"</t>
         </is>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n"/>
       <c r="E121" s="2" t="n"/>
       <c r="F121" s="2" t="n"/>
-      <c r="G121" s="5" t="n">
-        <v>1.6</v>
+      <c r="G121" s="4" t="n">
+        <v>0.2295</v>
       </c>
       <c r="H121" s="2" t="n"/>
-      <c r="I121" s="5" t="n">
-        <v>3.87</v>
+      <c r="I121" s="4" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>PVC-BUSHINGHS — FLUSH BUSHING (H x S)</t>
+          <t>PVC-1/4HS — 1/4 BEND, STREET (H x S)</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>2" x 1-1/2"</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>0.144161545215101</v>
-      </c>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n"/>
       <c r="E122" s="2" t="n"/>
-      <c r="F122" s="4" t="n">
-        <v>0.2554</v>
-      </c>
+      <c r="F122" s="2" t="n"/>
       <c r="G122" s="4" t="n">
-        <v>0.1215</v>
+        <v>0.3848</v>
       </c>
       <c r="H122" s="2" t="n"/>
       <c r="I122" s="4" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>PVC-BUSHINGHS — FLUSH BUSHING (H x S)</t>
+          <t>PVC-1/4HS — 1/4 BEND, STREET (H x S)</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>3" x 2"</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="n">
-        <v>0.534328358208955</v>
-      </c>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n"/>
       <c r="E123" s="2" t="n"/>
-      <c r="F123" s="4" t="n">
-        <v>0.8777</v>
-      </c>
-      <c r="G123" s="4" t="n">
-        <v>0.459</v>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="5" t="n">
+        <v>1.215</v>
       </c>
       <c r="H123" s="2" t="n"/>
       <c r="I123" s="5" t="n">
-        <v>1.15</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>PVC-BUSHINGHS — FLUSH BUSHING (H x S)</t>
+          <t>PVC-1/4HS — 1/4 BEND, STREET (H x S)</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>4" x 3"</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="n">
-        <v>1.00438981562774</v>
-      </c>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n"/>
       <c r="E124" s="2" t="n"/>
-      <c r="F124" s="5" t="n">
-        <v>1.587</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>0.6188</v>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="5" t="n">
+        <v>2.16</v>
       </c>
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="5" t="n">
-        <v>2.01</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>PVC-CAPSOC — CAP (SOC)</t>
+          <t>PVC-1/4LOWHEEL — 1/4 BEND W/ LOW HEEL INLET (H x H x H)</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="n">
-        <v>0.177699736611062</v>
+          <t>3" x 3" x 2"</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="n">
+        <v>1.6493</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" s="2" t="n"/>
-      <c r="F125" s="4" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="G125" s="4" t="n">
-        <v>0.0906</v>
+      <c r="F125" s="5" t="n">
+        <v>3.0971</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>1.3163</v>
       </c>
       <c r="H125" s="2" t="n"/>
-      <c r="I125" s="4" t="n">
-        <v>0.65</v>
+      <c r="I125" s="5" t="n">
+        <v>4.11</v>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>PVC-CAPSOC — CAP (SOC)</t>
+          <t>PVC-1/8HH — 1/8 BEND (H x H)</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
+          <t>1-1/2"</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0.274100087796313</v>
+        <v>0.3147</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" s="2" t="n"/>
       <c r="F126" s="4" t="n">
-        <v>0.5101</v>
+        <v>0.5091</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>0.1294</v>
+        <v>0.2273</v>
       </c>
       <c r="H126" s="2" t="n"/>
-      <c r="I126" s="5" t="n">
-        <v>1.48</v>
+      <c r="I126" s="4" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>PVC-CAPSOC — CAP (SOC)</t>
+          <t>PVC-1/8HH — 1/8 BEND (H x H)</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="n">
-        <v>0.8071992976295</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>0.306</v>
+      </c>
       <c r="E127" s="2" t="n"/>
-      <c r="F127" s="5" t="n">
-        <v>1.3594</v>
+      <c r="F127" s="4" t="n">
+        <v>0.7667</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>0.4286</v>
+        <v>0.3521</v>
       </c>
       <c r="H127" s="2" t="n"/>
-      <c r="I127" s="5" t="n">
-        <v>5.42</v>
+      <c r="I127" s="4" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>PVC-CAPSOC — CAP (SOC)</t>
+          <t>PVC-1/8HH — 1/8 BEND (H x H)</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="n">
-        <v>1.27164179104478</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>1.2464</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0.9091</v>
+      </c>
       <c r="E128" s="2" t="n"/>
       <c r="F128" s="5" t="n">
-        <v>2.0646</v>
-      </c>
-      <c r="G128" s="4" t="n">
-        <v>0.7538</v>
+        <v>2.0285</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>1.0462</v>
       </c>
       <c r="H128" s="2" t="n"/>
       <c r="I128" s="5" t="n">
-        <v>10.5</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>PVC-CLEANTEE — CLEANOUT TEE W/ C.O. PLUG (H x H)</t>
+          <t>PVC-1/8HH — 1/8 BEND (H x H)</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="n">
-        <v>0.653204565408253</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>2.4451</v>
+      </c>
+      <c r="D129" s="6" t="n">
+        <v>1.6227</v>
+      </c>
       <c r="E129" s="2" t="n"/>
       <c r="F129" s="5" t="n">
-        <v>1.1979</v>
-      </c>
-      <c r="G129" s="4" t="n">
-        <v>0.5625</v>
+        <v>4.0241</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>1.8675</v>
       </c>
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="5" t="n">
-        <v>2.87</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>PVC-CLEANTEE — CLEANOUT TEE W/ C.O. PLUG (H x H)</t>
+          <t>PVC-1/8HH — 1/8 BEND (H × H)</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="n">
-        <v>1.83107989464443</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="6" t="n">
+        <v>3.5094</v>
+      </c>
       <c r="E130" s="2" t="n"/>
-      <c r="F130" s="5" t="n">
-        <v>3.0288</v>
-      </c>
+      <c r="F130" s="2" t="n"/>
       <c r="G130" s="5" t="n">
-        <v>1.5638</v>
+        <v>3.6941</v>
       </c>
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="5" t="n">
-        <v>5.25</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>PVC-CLEANTEE — CLEANOUT TEE W/ C.O. PLUG (H x H)</t>
+          <t>PVC-1/8HH — 1/8 BEND (H × H)</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="n">
-        <v>3.86777875329236</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+          <t>8"</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="6" t="n">
+        <v>6.7353</v>
+      </c>
       <c r="E131" s="2" t="n"/>
-      <c r="F131" s="5" t="n">
-        <v>6.2695</v>
-      </c>
+      <c r="F131" s="2" t="n"/>
       <c r="G131" s="5" t="n">
-        <v>2.7788</v>
+        <v>7.0898</v>
       </c>
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="5" t="n">
-        <v>9.050000000000001</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>PVC-CLSTFLNGH — CLOSET FLANGE W/TEST PLATE (H)</t>
+          <t>PVC-1/8HS — 1/8 BEND STREET (H x S)</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>4" x 3"</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="n">
-        <v>1.13099209833187</v>
-      </c>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n"/>
       <c r="E132" s="2" t="n"/>
-      <c r="F132" s="5" t="n">
-        <v>1.9866</v>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>1.314</v>
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="4" t="n">
+        <v>0.2273</v>
       </c>
       <c r="H132" s="2" t="n"/>
-      <c r="I132" s="5" t="n">
-        <v>2.59</v>
+      <c r="I132" s="4" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>PVC-CPLNG — COUPLING (H x H)</t>
+          <t>PVC-1/8HS — 1/8 BEND STREET (H x S)</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="n">
-        <v>0.141352063213345</v>
-      </c>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n"/>
       <c r="E133" s="2" t="n"/>
-      <c r="F133" s="4" t="n">
-        <v>0.2514</v>
-      </c>
+      <c r="F133" s="2" t="n"/>
       <c r="G133" s="4" t="n">
-        <v>0.1193</v>
+        <v>0.35</v>
       </c>
       <c r="H133" s="2" t="n"/>
       <c r="I133" s="4" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>PVC-CPLNG — COUPLING (H x H)</t>
+          <t>PVC-1/8HS — 1/8 BEND STREET (H x S)</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="n">
-        <v>0.187532923617208</v>
-      </c>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n"/>
       <c r="E134" s="2" t="n"/>
-      <c r="F134" s="4" t="n">
-        <v>0.3666</v>
-      </c>
-      <c r="G134" s="4" t="n">
-        <v>0.1688</v>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="5" t="n">
+        <v>1.0013</v>
       </c>
       <c r="H134" s="2" t="n"/>
-      <c r="I134" s="4" t="n">
-        <v>0.34</v>
+      <c r="I134" s="5" t="n">
+        <v>2.22</v>
       </c>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>PVC-CPLNG — COUPLING (H x H)</t>
+          <t>PVC-1/8HS — 1/8 BEND STREET (H x S)</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="n">
-        <v>0.658823529411765</v>
-      </c>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n"/>
       <c r="E135" s="2" t="n"/>
-      <c r="F135" s="5" t="n">
-        <v>1.0898</v>
-      </c>
-      <c r="G135" s="4" t="n">
-        <v>0.5513</v>
+      <c r="F135" s="2" t="n"/>
+      <c r="G135" s="5" t="n">
+        <v>1.6</v>
       </c>
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="5" t="n">
-        <v>1.15</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>PVC-CPLNG — COUPLING (H x H)</t>
+          <t>PVC-45ELLSOC — 45° ELL (SOC × SOC)</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="n">
-        <v>1.11483757682177</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+          <t>10"</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="6" t="n">
+        <v>17.1475</v>
+      </c>
       <c r="E136" s="2" t="n"/>
-      <c r="F136" s="5" t="n">
-        <v>1.7419</v>
-      </c>
-      <c r="G136" s="4" t="n">
-        <v>0.945</v>
+      <c r="F136" s="2" t="n"/>
+      <c r="G136" s="5" t="n">
+        <v>18.05</v>
       </c>
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="5" t="n">
-        <v>2.13</v>
+        <v>68.59</v>
       </c>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H x H)</t>
+          <t>PVC-BUSHINGHS — FLUSH BUSHING (H x S)</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>10x6"</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="6" t="n">
-        <v>8.9537</v>
-      </c>
+          <t>2" x 1-1/2"</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" s="2" t="n"/>
-      <c r="F137" s="2" t="n"/>
-      <c r="G137" s="5" t="n">
-        <v>9.425000000000001</v>
+      <c r="F137" s="4" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>0.1215</v>
       </c>
       <c r="H137" s="2" t="n"/>
-      <c r="I137" s="5" t="n">
-        <v>35.82</v>
+      <c r="I137" s="4" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H x H)</t>
+          <t>PVC-BUSHINGHS — FLUSH BUSHING (H x S)</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>10x8"</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="6" t="n">
-        <v>8.9537</v>
-      </c>
+          <t>3" x 2"</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" s="2" t="n"/>
-      <c r="F138" s="2" t="n"/>
-      <c r="G138" s="5" t="n">
-        <v>9.425000000000001</v>
+      <c r="F138" s="4" t="n">
+        <v>0.8777</v>
+      </c>
+      <c r="G138" s="4" t="n">
+        <v>0.459</v>
       </c>
       <c r="H138" s="2" t="n"/>
       <c r="I138" s="5" t="n">
-        <v>35.82</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H x H)</t>
+          <t>PVC-BUSHINGHS — FLUSH BUSHING (H x S)</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>2" x 1-1/2"</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="3" t="n">
-        <v>0.1486</v>
-      </c>
+          <t>4" x 3"</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="n">
+        <v>1.0044</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" s="2" t="n"/>
-      <c r="F139" s="2" t="n"/>
+      <c r="F139" s="5" t="n">
+        <v>1.587</v>
+      </c>
       <c r="G139" s="4" t="n">
-        <v>0.171</v>
+        <v>0.6188</v>
       </c>
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="5" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H x H)</t>
+          <t>PVC-CAPSOC — CAP (SOC)</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>3" x 2"</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="3" t="n">
-        <v>0.4272</v>
-      </c>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" s="2" t="n"/>
-      <c r="F140" s="2" t="n"/>
+      <c r="F140" s="4" t="n">
+        <v>0.342</v>
+      </c>
       <c r="G140" s="4" t="n">
-        <v>0.4916</v>
+        <v>0.0906</v>
       </c>
       <c r="H140" s="2" t="n"/>
-      <c r="I140" s="5" t="n">
-        <v>1.84</v>
+      <c r="I140" s="4" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H × H)</t>
+          <t>PVC-CAPSOC — CAP (SOC)</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>4" x 2"</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="3" t="n">
-        <v>0.7527</v>
-      </c>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" s="2" t="n"/>
-      <c r="F141" s="2" t="n"/>
+      <c r="F141" s="4" t="n">
+        <v>0.5101</v>
+      </c>
       <c r="G141" s="4" t="n">
-        <v>0.7923</v>
+        <v>0.1294</v>
       </c>
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="5" t="n">
-        <v>3.01</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H x H)</t>
+          <t>PVC-CAPSOC — CAP (SOC)</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>4" x 3"</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="3" t="n">
-        <v>0.8407</v>
-      </c>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>0.8072</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" s="2" t="n"/>
-      <c r="F142" s="2" t="n"/>
+      <c r="F142" s="5" t="n">
+        <v>1.3594</v>
+      </c>
       <c r="G142" s="4" t="n">
-        <v>0.9675</v>
+        <v>0.4286</v>
       </c>
       <c r="H142" s="2" t="n"/>
       <c r="I142" s="5" t="n">
-        <v>3.85</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H × H)</t>
+          <t>PVC-CAPSOC — CAP (SOC)</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>6" x 3"</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="6" t="n">
-        <v>3.021</v>
-      </c>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="n">
+        <v>1.2716</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" s="2" t="n"/>
-      <c r="F143" s="2" t="n"/>
-      <c r="G143" s="5" t="n">
-        <v>3.18</v>
+      <c r="F143" s="5" t="n">
+        <v>2.0646</v>
+      </c>
+      <c r="G143" s="4" t="n">
+        <v>0.7538</v>
       </c>
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="5" t="n">
-        <v>12.08</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H × H)</t>
+          <t>PVC-CLEANTEE — CLEANOUT TEE W/ C.O. PLUG (H x H)</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>6" x 4"</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="6" t="n">
-        <v>1.9453</v>
-      </c>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>0.6532</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" s="2" t="n"/>
-      <c r="F144" s="2" t="n"/>
-      <c r="G144" s="5" t="n">
-        <v>2.0477</v>
+      <c r="F144" s="5" t="n">
+        <v>1.1979</v>
+      </c>
+      <c r="G144" s="4" t="n">
+        <v>0.5625</v>
       </c>
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="5" t="n">
-        <v>7.78</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H × H)</t>
+          <t>PVC-CLEANTEE — CLEANOUT TEE W/ C.O. PLUG (H x H)</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>8" x 6"</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="6" t="n">
-        <v>4.1155</v>
-      </c>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="n">
+        <v>1.8311</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" s="2" t="n"/>
-      <c r="F145" s="2" t="n"/>
+      <c r="F145" s="5" t="n">
+        <v>3.0288</v>
+      </c>
       <c r="G145" s="5" t="n">
-        <v>4.3321</v>
+        <v>1.5638</v>
       </c>
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="5" t="n">
-        <v>16.46</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>PVC-MADPTR — MALE ADAPTER (MPT x H)</t>
+          <t>PVC-CLEANTEE — CLEANOUT TEE W/ C.O. PLUG (H x H)</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>0.156628621597893</v>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="n">
+        <v>3.8678</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" s="2" t="n"/>
-      <c r="F146" s="4" t="n">
-        <v>0.2445</v>
-      </c>
-      <c r="G146" s="4" t="n">
-        <v>0.1001</v>
+      <c r="F146" s="5" t="n">
+        <v>6.2695</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>2.7788</v>
       </c>
       <c r="H146" s="2" t="n"/>
-      <c r="I146" s="4" t="n">
-        <v>0.55</v>
+      <c r="I146" s="5" t="n">
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>PVC-MADPTR — MALE ADAPTER (MPT x H)</t>
+          <t>PVC-CLSTFLNG-ADJ — CLOSET FLANGE W/ADJUSTABLE METAL RING (H)</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="n">
-        <v>0.251799824407375</v>
-      </c>
+          <t>4" x 3"</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n"/>
       <c r="E147" s="2" t="n"/>
-      <c r="F147" s="4" t="n">
-        <v>0.4093</v>
-      </c>
-      <c r="G147" s="4" t="n">
-        <v>0.1328</v>
+      <c r="F147" s="2" t="n"/>
+      <c r="G147" s="5" t="n">
+        <v>1.0575</v>
       </c>
       <c r="H147" s="2" t="n"/>
-      <c r="I147" s="4" t="n">
-        <v>0.65</v>
-      </c>
+      <c r="I147" s="2" t="n"/>
     </row>
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>PVC-PTRAP — P-TRAP (H x H)</t>
+          <t>PVC-CLSTFLNGH — CLOSET FLANGE W/TEST PLATE (H)</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n"/>
+          <t>4" x 3"</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="n">
+        <v>1.131</v>
+      </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" s="2" t="n"/>
-      <c r="F148" s="2" t="n"/>
-      <c r="G148" s="4" t="n">
-        <v>0.6188</v>
+      <c r="F148" s="5" t="n">
+        <v>1.9866</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>1.314</v>
       </c>
       <c r="H148" s="2" t="n"/>
       <c r="I148" s="5" t="n">
-        <v>3.89</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>PVC-PTRAP — P-TRAP (H x H)</t>
+          <t>PVC-CPLNG — COUPLING (H x H)</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="n">
-        <v>1.2270412642669</v>
-      </c>
-      <c r="D149" s="3" t="n">
-        <v>0.9434</v>
-      </c>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>0.1414</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" s="2" t="n"/>
-      <c r="F149" s="5" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="G149" s="5" t="n">
-        <v>1.0913</v>
+      <c r="F149" s="4" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="G149" s="4" t="n">
+        <v>0.1193</v>
       </c>
       <c r="H149" s="2" t="n"/>
-      <c r="I149" s="5" t="n">
-        <v>2.35</v>
+      <c r="I149" s="4" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>PVC-PTRAP — P-TRAP (H x H)</t>
+          <t>PVC-CPLNG — COUPLING (H x H)</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n"/>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>0.1875</v>
+      </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" s="2" t="n"/>
-      <c r="F150" s="2" t="n"/>
-      <c r="G150" s="5" t="n">
-        <v>2.9138</v>
+      <c r="F150" s="4" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="G150" s="4" t="n">
+        <v>0.1688</v>
       </c>
       <c r="H150" s="2" t="n"/>
-      <c r="I150" s="5" t="n">
-        <v>15.05</v>
+      <c r="I150" s="4" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>PVC-PTRAP — P-TRAP (H x H)</t>
+          <t>PVC-CPLNG — COUPLING (H x H)</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="n"/>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>0.6588000000000001</v>
+      </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" s="2" t="n"/>
-      <c r="F151" s="2" t="n"/>
-      <c r="G151" s="5" t="n">
-        <v>5.1863</v>
+      <c r="F151" s="5" t="n">
+        <v>1.0898</v>
+      </c>
+      <c r="G151" s="4" t="n">
+        <v>0.5513</v>
       </c>
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="5" t="n">
-        <v>26.75</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PVC-PTRAPLOW — P-TRAP, LOW PROFILE(HxH)</t>
+          <t>PVC-CPLNG — COUPLING (H x H)</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n"/>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="n">
+        <v>1.1148</v>
+      </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" s="2" t="n"/>
-      <c r="F152" s="2" t="n"/>
+      <c r="F152" s="5" t="n">
+        <v>1.7419</v>
+      </c>
       <c r="G152" s="4" t="n">
-        <v>0.6075</v>
+        <v>0.945</v>
       </c>
       <c r="H152" s="2" t="n"/>
       <c r="I152" s="5" t="n">
-        <v>1.22</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PVC-PTRAPLOW — P-TRAP, LOW PROFILE(HxH)</t>
+          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H X H)</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
+          <t>10" x 6"</t>
         </is>
       </c>
       <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n"/>
+      <c r="D153" s="6" t="n">
+        <v>8.9537</v>
+      </c>
       <c r="E153" s="2" t="n"/>
       <c r="F153" s="2" t="n"/>
       <c r="G153" s="5" t="n">
-        <v>1.0238</v>
+        <v>9.425000000000001</v>
       </c>
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="5" t="n">
-        <v>5.25</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>PVC-PTRAPLOW — P-TRAP, LOW PROFILE(HxH)</t>
+          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H X H)</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
+          <t>10" x 8"</t>
         </is>
       </c>
       <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n"/>
+      <c r="D154" s="6" t="n">
+        <v>8.9537</v>
+      </c>
       <c r="E154" s="2" t="n"/>
       <c r="F154" s="2" t="n"/>
       <c r="G154" s="5" t="n">
-        <v>2.9813</v>
+        <v>9.425000000000001</v>
       </c>
       <c r="H154" s="2" t="n"/>
       <c r="I154" s="5" t="n">
-        <v>16.25</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>PVC-PTRAPLOW — P-TRAP, LOW PROFILE(HxH)</t>
+          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H x H)</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
+          <t>2" x 1-1/2"</t>
         </is>
       </c>
       <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n"/>
+      <c r="D155" s="3" t="n">
+        <v>0.1486</v>
+      </c>
       <c r="E155" s="2" t="n"/>
       <c r="F155" s="2" t="n"/>
-      <c r="G155" s="5" t="n">
-        <v>5.2763</v>
+      <c r="G155" s="4" t="n">
+        <v>0.171</v>
       </c>
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="5" t="n">
-        <v>38</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEE — SANITARY TEE (ALL HUB)</t>
+          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H x H)</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="n">
-        <v>0.415452151009658</v>
-      </c>
+          <t>3" x 2"</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n"/>
       <c r="D156" s="3" t="n">
-        <v>0.3059</v>
+        <v>0.4272</v>
       </c>
       <c r="E156" s="2" t="n"/>
-      <c r="F156" s="4" t="n">
-        <v>0.7035</v>
-      </c>
+      <c r="F156" s="2" t="n"/>
       <c r="G156" s="4" t="n">
-        <v>0.3623</v>
+        <v>0.4916</v>
       </c>
       <c r="H156" s="2" t="n"/>
-      <c r="I156" s="4" t="n">
-        <v>0.91</v>
+      <c r="I156" s="5" t="n">
+        <v>1.84</v>
       </c>
     </row>
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEE — SANITARY TEE (ALL HUB)</t>
+          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H × H)</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="n">
-        <v>0.671466198419666</v>
-      </c>
+          <t>4" x 2"</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n"/>
       <c r="D157" s="3" t="n">
-        <v>0.4845</v>
+        <v>0.7527</v>
       </c>
       <c r="E157" s="2" t="n"/>
-      <c r="F157" s="5" t="n">
-        <v>1.224</v>
-      </c>
+      <c r="F157" s="2" t="n"/>
       <c r="G157" s="4" t="n">
-        <v>0.5737</v>
+        <v>0.7923</v>
       </c>
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="5" t="n">
-        <v>1.32</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEE — SANITARY TEE (ALL HUB)</t>
+          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H x H)</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C158" s="5" t="n">
-        <v>2.03810359964881</v>
-      </c>
-      <c r="D158" s="6" t="n">
-        <v>1.5054</v>
+          <t>4" x 3"</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="3" t="n">
+        <v>0.8407</v>
       </c>
       <c r="E158" s="2" t="n"/>
-      <c r="F158" s="5" t="n">
-        <v>3.3761</v>
-      </c>
-      <c r="G158" s="5" t="n">
-        <v>1.7325</v>
+      <c r="F158" s="2" t="n"/>
+      <c r="G158" s="4" t="n">
+        <v>0.9675</v>
       </c>
       <c r="H158" s="2" t="n"/>
       <c r="I158" s="5" t="n">
-        <v>6.99</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEE — SANITARY TEE (ALL HUB)</t>
+          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H × H)</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="C159" s="5" t="n">
-        <v>3.5153643546971</v>
-      </c>
+          <t>6" x 3"</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n"/>
       <c r="D159" s="6" t="n">
-        <v>2.6505</v>
+        <v>3.021</v>
       </c>
       <c r="E159" s="2" t="n"/>
-      <c r="F159" s="5" t="n">
-        <v>5.7655</v>
-      </c>
+      <c r="F159" s="2" t="n"/>
       <c r="G159" s="5" t="n">
-        <v>3.1387</v>
+        <v>3.18</v>
       </c>
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="5" t="n">
-        <v>14.75</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEEDBL — DOUBLE SANITARY TEE, REDUCING (ALL HUB)</t>
+          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H × H)</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>2" x 2" x 1-1/2" x 1-1/2"</t>
+          <t>6" x 4"</t>
         </is>
       </c>
       <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n"/>
+      <c r="D160" s="6" t="n">
+        <v>1.9453</v>
+      </c>
       <c r="E160" s="2" t="n"/>
       <c r="F160" s="2" t="n"/>
-      <c r="G160" s="4" t="n">
-        <v>0.5625</v>
+      <c r="G160" s="5" t="n">
+        <v>2.0477</v>
       </c>
       <c r="H160" s="2" t="n"/>
       <c r="I160" s="5" t="n">
-        <v>4.25</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
+          <t>PVC-INCREDHH — PIPE INCREASER-REDUCER (H × H)</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>2" x 1-1/2"</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="n">
-        <v>0.690956979806848</v>
-      </c>
-      <c r="D161" s="3" t="n">
-        <v>0.419</v>
+          <t>8" x 6"</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="6" t="n">
+        <v>4.1155</v>
       </c>
       <c r="E161" s="2" t="n"/>
-      <c r="F161" s="5" t="n">
-        <v>1.2958</v>
-      </c>
-      <c r="G161" s="4" t="n">
-        <v>0.6758999999999999</v>
+      <c r="F161" s="2" t="n"/>
+      <c r="G161" s="5" t="n">
+        <v>4.3321</v>
       </c>
       <c r="H161" s="2" t="n"/>
       <c r="I161" s="5" t="n">
-        <v>1.68</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
+          <t>PVC-MADPTR — MALE ADAPTER (MPT x H)</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>2" x 1-1/2" x 1-1/2"</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n"/>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>0.1566</v>
+      </c>
       <c r="D162" s="2" t="n"/>
       <c r="E162" s="2" t="n"/>
-      <c r="F162" s="2" t="n"/>
+      <c r="F162" s="4" t="n">
+        <v>0.2445</v>
+      </c>
       <c r="G162" s="4" t="n">
-        <v>0.4511</v>
+        <v>0.1001</v>
       </c>
       <c r="H162" s="2" t="n"/>
-      <c r="I162" s="5" t="n">
-        <v>1.15</v>
+      <c r="I162" s="4" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
+          <t>PVC-MADPTR — MALE ADAPTER (MPT x H)</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>2" x 1-1/2" x 2"</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n"/>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>0.2518</v>
+      </c>
       <c r="D163" s="2" t="n"/>
       <c r="E163" s="2" t="n"/>
-      <c r="F163" s="2" t="n"/>
+      <c r="F163" s="4" t="n">
+        <v>0.4093</v>
+      </c>
       <c r="G163" s="4" t="n">
-        <v>0.5153</v>
+        <v>0.1328</v>
       </c>
       <c r="H163" s="2" t="n"/>
-      <c r="I163" s="5" t="n">
-        <v>1.53</v>
+      <c r="I163" s="4" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
+          <t>PVC-PTRAP — P-TRAP (H x H)</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>2" x 2" x 1-1/2"</t>
+          <t>1-1/2"</t>
         </is>
       </c>
       <c r="C164" s="2" t="n"/>
@@ -4598,130 +4558,120 @@
       <c r="E164" s="2" t="n"/>
       <c r="F164" s="2" t="n"/>
       <c r="G164" s="4" t="n">
-        <v>0.4714</v>
+        <v>0.6188</v>
       </c>
       <c r="H164" s="2" t="n"/>
       <c r="I164" s="5" t="n">
-        <v>1.16</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
+          <t>PVC-PTRAP — P-TRAP (H x H)</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>3" x 2"</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="6" t="n">
-        <v>1.05</v>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>0.9434</v>
       </c>
       <c r="E165" s="2" t="n"/>
-      <c r="F165" s="2" t="n"/>
+      <c r="F165" s="5" t="n">
+        <v>2.247</v>
+      </c>
       <c r="G165" s="5" t="n">
-        <v>1.705</v>
+        <v>1.0913</v>
       </c>
       <c r="H165" s="2" t="n"/>
       <c r="I165" s="5" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
+          <t>PVC-PTRAP — P-TRAP (H x H)</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>3" x 3" x 2"</t>
+          <t>3"</t>
         </is>
       </c>
       <c r="C166" s="2" t="n"/>
-      <c r="D166" s="6" t="n">
-        <v>1.0264</v>
-      </c>
+      <c r="D166" s="2" t="n"/>
       <c r="E166" s="2" t="n"/>
       <c r="F166" s="2" t="n"/>
       <c r="G166" s="5" t="n">
-        <v>1.1812</v>
+        <v>2.9138</v>
       </c>
       <c r="H166" s="2" t="n"/>
       <c r="I166" s="5" t="n">
-        <v>5.75</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
+          <t>PVC-PTRAP — P-TRAP (H x H)</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>4" x 4" x 2"</t>
-        </is>
-      </c>
-      <c r="C167" s="5" t="n">
-        <v>2.60474100087796</v>
-      </c>
-      <c r="D167" s="6" t="n">
-        <v>1.3979</v>
-      </c>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n"/>
       <c r="E167" s="2" t="n"/>
-      <c r="F167" s="5" t="n">
-        <v>4.3402</v>
-      </c>
+      <c r="F167" s="2" t="n"/>
       <c r="G167" s="5" t="n">
-        <v>1.4715</v>
+        <v>5.1863</v>
       </c>
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="5" t="n">
-        <v>5.59</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
+          <t>PVC-PTRAPLOW — P-TRAP, LOW PROFILE(HxH)</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>4" x 4" x 3"</t>
-        </is>
-      </c>
-      <c r="C168" s="5" t="n">
-        <v>3.48323090430202</v>
-      </c>
-      <c r="D168" s="6" t="n">
-        <v>2.0529</v>
-      </c>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n"/>
       <c r="E168" s="2" t="n"/>
-      <c r="F168" s="5" t="n">
-        <v>5.8016</v>
-      </c>
-      <c r="G168" s="5" t="n">
-        <v>2.3625</v>
+      <c r="F168" s="2" t="n"/>
+      <c r="G168" s="4" t="n">
+        <v>0.6075</v>
       </c>
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="5" t="n">
-        <v>9.65</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYEDBL — REDUCING DOUBLE WYE (ALL HUB)</t>
+          <t>PVC-PTRAPLOW — P-TRAP, LOW PROFILE(HxH)</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>3" x 3" x 2" x 2"</t>
+          <t>2"</t>
         </is>
       </c>
       <c r="C169" s="2" t="n"/>
@@ -4729,362 +4679,1577 @@
       <c r="E169" s="2" t="n"/>
       <c r="F169" s="2" t="n"/>
       <c r="G169" s="5" t="n">
-        <v>1.665</v>
+        <v>1.0238</v>
       </c>
       <c r="H169" s="2" t="n"/>
       <c r="I169" s="5" t="n">
-        <v>6.55</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYEHUB — WYE (ALL HUB)</t>
+          <t>PVC-PTRAPLOW — P-TRAP, LOW PROFILE(HxH)</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>1-1/2"</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="n">
-        <v>0.549780509218613</v>
-      </c>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n"/>
       <c r="D170" s="2" t="n"/>
       <c r="E170" s="2" t="n"/>
-      <c r="F170" s="4" t="n">
-        <v>0.954</v>
-      </c>
-      <c r="G170" s="4" t="n">
-        <v>0.4545</v>
+      <c r="F170" s="2" t="n"/>
+      <c r="G170" s="5" t="n">
+        <v>2.9813</v>
       </c>
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="5" t="n">
-        <v>1.72</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYEHUB — WYE (ALL HUB)</t>
+          <t>PVC-PTRAPLOW — P-TRAP, LOW PROFILE(HxH)</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="n">
-        <v>0.832309043020193</v>
-      </c>
-      <c r="D171" s="3" t="n">
-        <v>0.5963000000000001</v>
-      </c>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n"/>
       <c r="E171" s="2" t="n"/>
-      <c r="F171" s="5" t="n">
-        <v>1.4856</v>
-      </c>
-      <c r="G171" s="4" t="n">
-        <v>0.6863</v>
+      <c r="F171" s="2" t="n"/>
+      <c r="G171" s="5" t="n">
+        <v>5.2763</v>
       </c>
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="5" t="n">
-        <v>3.6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYEHUB — WYE (ALL HUB)</t>
+          <t>PVC-SANTEE — SANITARY TEE (ALL HUB)</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="C172" s="5" t="n">
-        <v>2.46338893766462</v>
-      </c>
-      <c r="D172" s="6" t="n">
-        <v>1.7987</v>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>0.3059</v>
       </c>
       <c r="E172" s="2" t="n"/>
-      <c r="F172" s="5" t="n">
-        <v>4.1381</v>
-      </c>
-      <c r="G172" s="5" t="n">
-        <v>2.07</v>
+      <c r="F172" s="4" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="G172" s="4" t="n">
+        <v>0.3623</v>
       </c>
       <c r="H172" s="2" t="n"/>
-      <c r="I172" s="5" t="n">
-        <v>7.19</v>
+      <c r="I172" s="4" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYEHUB — WYE (ALL HUB)</t>
+          <t>PVC-SANTEE — SANITARY TEE (ALL HUB)</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="C173" s="5" t="n">
-        <v>4.42598770851624</v>
-      </c>
-      <c r="D173" s="6" t="n">
-        <v>3.2748</v>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="n">
+        <v>0.6715</v>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>0.4845</v>
       </c>
       <c r="E173" s="2" t="n"/>
       <c r="F173" s="5" t="n">
-        <v>7.0677</v>
-      </c>
-      <c r="G173" s="5" t="n">
-        <v>3.7687</v>
+        <v>1.224</v>
+      </c>
+      <c r="G173" s="4" t="n">
+        <v>0.5737</v>
       </c>
       <c r="H173" s="2" t="n"/>
       <c r="I173" s="5" t="n">
-        <v>13.1</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYEHUB — WYE (ALL HUB)</t>
+          <t>PVC-SANTEE — SANITARY TEE (ALL HUB)</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>6"</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n"/>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="n">
+        <v>2.0381</v>
+      </c>
       <c r="D174" s="6" t="n">
-        <v>7.5662</v>
+        <v>1.5054</v>
       </c>
       <c r="E174" s="2" t="n"/>
-      <c r="F174" s="2" t="n"/>
+      <c r="F174" s="5" t="n">
+        <v>3.3761</v>
+      </c>
       <c r="G174" s="5" t="n">
-        <v>7.9645</v>
+        <v>1.7325</v>
       </c>
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="5" t="n">
-        <v>30.26</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="175" ht="22" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+          <t>PVC-SANTEE — SANITARY TEE (ALL HUB)</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>3" x 3" x 2"</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n"/>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="n">
+        <v>3.5154</v>
+      </c>
       <c r="D175" s="6" t="n">
-        <v>1.2904</v>
+        <v>2.6505</v>
       </c>
       <c r="E175" s="2" t="n"/>
-      <c r="F175" s="2" t="n"/>
+      <c r="F175" s="5" t="n">
+        <v>5.7655</v>
+      </c>
       <c r="G175" s="5" t="n">
-        <v>1.485</v>
+        <v>3.1387</v>
       </c>
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="5" t="n">
-        <v>7.05</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="176" ht="22" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+          <t>PVC-SANTEEDBL — DOUBLE SANITARY TEE, REDUCING (ALL HUB)</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>4" x 4" x 2"</t>
-        </is>
-      </c>
-      <c r="C176" s="5" t="n">
-        <v>2.60474100087796</v>
-      </c>
-      <c r="D176" s="6" t="n">
-        <v>1.8964</v>
-      </c>
+          <t>2" x 2" x 1-1/2" x 1-1/2"</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n"/>
       <c r="E176" s="2" t="n"/>
-      <c r="F176" s="5" t="n">
-        <v>4.3402</v>
-      </c>
-      <c r="G176" s="5" t="n">
-        <v>2.1825</v>
+      <c r="F176" s="2" t="n"/>
+      <c r="G176" s="4" t="n">
+        <v>0.5625</v>
       </c>
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="5" t="n">
-        <v>5.3</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="177" ht="22" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>4" x 4" x 3"</t>
-        </is>
-      </c>
-      <c r="C177" s="5" t="n">
-        <v>3.48323090430202</v>
-      </c>
-      <c r="D177" s="6" t="n">
-        <v>2.5905</v>
+          <t>2" x 1-1/2"</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>0.419</v>
       </c>
       <c r="E177" s="2" t="n"/>
       <c r="F177" s="5" t="n">
-        <v>5.8016</v>
-      </c>
-      <c r="G177" s="5" t="n">
-        <v>2.9813</v>
+        <v>1.2958</v>
+      </c>
+      <c r="G177" s="4" t="n">
+        <v>0.6758999999999999</v>
       </c>
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="5" t="n">
-        <v>6.71</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="178" ht="22" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>6" x 6" x 2"</t>
+          <t>2" x 1-1/2" x 1-1/2"</t>
         </is>
       </c>
       <c r="C178" s="2" t="n"/>
-      <c r="D178" s="6" t="n">
-        <v>4.5554</v>
-      </c>
+      <c r="D178" s="2" t="n"/>
       <c r="E178" s="2" t="n"/>
       <c r="F178" s="2" t="n"/>
-      <c r="G178" s="5" t="n">
-        <v>4.7951</v>
+      <c r="G178" s="4" t="n">
+        <v>0.4511</v>
       </c>
       <c r="H178" s="2" t="n"/>
       <c r="I178" s="5" t="n">
-        <v>18.22</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="179" ht="22" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>6" x 6" x 3"</t>
+          <t>2" x 1-1/2" x 2"</t>
         </is>
       </c>
       <c r="C179" s="2" t="n"/>
-      <c r="D179" s="6" t="n">
-        <v>4.8095</v>
-      </c>
+      <c r="D179" s="2" t="n"/>
       <c r="E179" s="2" t="n"/>
       <c r="F179" s="2" t="n"/>
-      <c r="G179" s="5" t="n">
-        <v>5.0627</v>
+      <c r="G179" s="4" t="n">
+        <v>0.5153</v>
       </c>
       <c r="H179" s="2" t="n"/>
       <c r="I179" s="5" t="n">
-        <v>19.24</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="180" ht="22" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>6" x 6" x 4"</t>
+          <t>2" x 2" x 1-1/2"</t>
         </is>
       </c>
       <c r="C180" s="2" t="n"/>
-      <c r="D180" s="6" t="n">
-        <v>5.3472</v>
-      </c>
+      <c r="D180" s="2" t="n"/>
       <c r="E180" s="2" t="n"/>
       <c r="F180" s="2" t="n"/>
-      <c r="G180" s="5" t="n">
-        <v>5.6286</v>
+      <c r="G180" s="4" t="n">
+        <v>0.4714</v>
       </c>
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="5" t="n">
-        <v>21.39</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="181" ht="22" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>8" x 8" x 4"</t>
+          <t>3" x 2"</t>
         </is>
       </c>
       <c r="C181" s="2" t="n"/>
       <c r="D181" s="6" t="n">
-        <v>8.993499999999999</v>
+        <v>1.05</v>
       </c>
       <c r="E181" s="2" t="n"/>
       <c r="F181" s="2" t="n"/>
       <c r="G181" s="5" t="n">
-        <v>9.466799999999999</v>
+        <v>1.705</v>
       </c>
       <c r="H181" s="2" t="n"/>
       <c r="I181" s="5" t="n">
-        <v>35.97</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="182" ht="22" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>8" x 8" x 6"</t>
+          <t>3" x 3" x 2"</t>
         </is>
       </c>
       <c r="C182" s="2" t="n"/>
       <c r="D182" s="6" t="n">
-        <v>11.6915</v>
+        <v>1.0264</v>
       </c>
       <c r="E182" s="2" t="n"/>
       <c r="F182" s="2" t="n"/>
       <c r="G182" s="5" t="n">
-        <v>12.3068</v>
+        <v>1.1812</v>
       </c>
       <c r="H182" s="2" t="n"/>
       <c r="I182" s="5" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>4" x 4" x 2"</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>2.6047</v>
+      </c>
+      <c r="D183" s="6" t="n">
+        <v>1.3979</v>
+      </c>
+      <c r="E183" s="2" t="n"/>
+      <c r="F183" s="5" t="n">
+        <v>4.3402</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>1.4715</v>
+      </c>
+      <c r="H183" s="2" t="n"/>
+      <c r="I183" s="5" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>PVC-SANTEERED — REDUCING SANITARY TEE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>4" x 4" x 3"</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>3.4832</v>
+      </c>
+      <c r="D184" s="6" t="n">
+        <v>2.0529</v>
+      </c>
+      <c r="E184" s="2" t="n"/>
+      <c r="F184" s="5" t="n">
+        <v>5.8016</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>2.3625</v>
+      </c>
+      <c r="H184" s="2" t="n"/>
+      <c r="I184" s="5" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="185" ht="22" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYEDBL — REDUCING DOUBLE WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>3" x 3" x 2" x 2"</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="n"/>
+      <c r="F185" s="2" t="n"/>
+      <c r="G185" s="5" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="H185" s="2" t="n"/>
+      <c r="I185" s="5" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="186" ht="22" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYEHUB — WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="n"/>
+      <c r="F186" s="4" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="G186" s="4" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="H186" s="2" t="n"/>
+      <c r="I186" s="5" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYEHUB — WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="n">
+        <v>0.8323</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>0.5963000000000001</v>
+      </c>
+      <c r="E187" s="2" t="n"/>
+      <c r="F187" s="5" t="n">
+        <v>1.4856</v>
+      </c>
+      <c r="G187" s="4" t="n">
+        <v>0.6863</v>
+      </c>
+      <c r="H187" s="2" t="n"/>
+      <c r="I187" s="5" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="188" ht="22" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYEHUB — WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>2.4634</v>
+      </c>
+      <c r="D188" s="6" t="n">
+        <v>1.7987</v>
+      </c>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="5" t="n">
+        <v>4.1381</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H188" s="2" t="n"/>
+      <c r="I188" s="5" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="189" ht="22" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYEHUB — WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>4.426</v>
+      </c>
+      <c r="D189" s="6" t="n">
+        <v>3.2748</v>
+      </c>
+      <c r="E189" s="2" t="n"/>
+      <c r="F189" s="5" t="n">
+        <v>7.0677</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>3.7687</v>
+      </c>
+      <c r="H189" s="2" t="n"/>
+      <c r="I189" s="5" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYEHUB — WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n"/>
+      <c r="D190" s="6" t="n">
+        <v>7.5662</v>
+      </c>
+      <c r="E190" s="2" t="n"/>
+      <c r="F190" s="2" t="n"/>
+      <c r="G190" s="5" t="n">
+        <v>7.9645</v>
+      </c>
+      <c r="H190" s="2" t="n"/>
+      <c r="I190" s="5" t="n">
+        <v>30.26</v>
+      </c>
+    </row>
+    <row r="191" ht="22" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>3" x 3" x 2"</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n"/>
+      <c r="D191" s="6" t="n">
+        <v>1.2904</v>
+      </c>
+      <c r="E191" s="2" t="n"/>
+      <c r="F191" s="2" t="n"/>
+      <c r="G191" s="5" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="H191" s="2" t="n"/>
+      <c r="I191" s="5" t="n">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="192" ht="22" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>4" x 4" x 2"</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="n">
+        <v>2.6047</v>
+      </c>
+      <c r="D192" s="6" t="n">
+        <v>1.8964</v>
+      </c>
+      <c r="E192" s="2" t="n"/>
+      <c r="F192" s="5" t="n">
+        <v>4.3402</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>2.1825</v>
+      </c>
+      <c r="H192" s="2" t="n"/>
+      <c r="I192" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>4" x 4" x 3"</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="n">
+        <v>3.4832</v>
+      </c>
+      <c r="D193" s="6" t="n">
+        <v>2.5905</v>
+      </c>
+      <c r="E193" s="2" t="n"/>
+      <c r="F193" s="5" t="n">
+        <v>5.8016</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>2.9813</v>
+      </c>
+      <c r="H193" s="2" t="n"/>
+      <c r="I193" s="5" t="n">
+        <v>6.71</v>
+      </c>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>6" x 6" x 2"</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n"/>
+      <c r="D194" s="6" t="n">
+        <v>4.5554</v>
+      </c>
+      <c r="E194" s="2" t="n"/>
+      <c r="F194" s="2" t="n"/>
+      <c r="G194" s="5" t="n">
+        <v>4.7951</v>
+      </c>
+      <c r="H194" s="2" t="n"/>
+      <c r="I194" s="5" t="n">
+        <v>18.22</v>
+      </c>
+    </row>
+    <row r="195" ht="22" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>6" x 6" x 3"</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n"/>
+      <c r="D195" s="6" t="n">
+        <v>4.8095</v>
+      </c>
+      <c r="E195" s="2" t="n"/>
+      <c r="F195" s="2" t="n"/>
+      <c r="G195" s="5" t="n">
+        <v>5.0627</v>
+      </c>
+      <c r="H195" s="2" t="n"/>
+      <c r="I195" s="5" t="n">
+        <v>19.24</v>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>6" x 6" x 4"</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="n"/>
+      <c r="D196" s="6" t="n">
+        <v>5.3472</v>
+      </c>
+      <c r="E196" s="2" t="n"/>
+      <c r="F196" s="2" t="n"/>
+      <c r="G196" s="5" t="n">
+        <v>5.6286</v>
+      </c>
+      <c r="H196" s="2" t="n"/>
+      <c r="I196" s="5" t="n">
+        <v>21.39</v>
+      </c>
+    </row>
+    <row r="197" ht="22" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>8" x 8" x 4"</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="6" t="n">
+        <v>8.993499999999999</v>
+      </c>
+      <c r="E197" s="2" t="n"/>
+      <c r="F197" s="2" t="n"/>
+      <c r="G197" s="5" t="n">
+        <v>9.466799999999999</v>
+      </c>
+      <c r="H197" s="2" t="n"/>
+      <c r="I197" s="5" t="n">
+        <v>35.97</v>
+      </c>
+    </row>
+    <row r="198" ht="22" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>PVC-WYERED — REDUCING WYE (ALL HUB)</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>8" x 8" x 6"</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n"/>
+      <c r="D198" s="6" t="n">
+        <v>11.6915</v>
+      </c>
+      <c r="E198" s="2" t="n"/>
+      <c r="F198" s="2" t="n"/>
+      <c r="G198" s="5" t="n">
+        <v>12.3068</v>
+      </c>
+      <c r="H198" s="2" t="n"/>
+      <c r="I198" s="5" t="n">
         <v>46.77</v>
       </c>
     </row>
+    <row r="199" ht="22" customHeight="1">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-CPLNG — COUPLING</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="n"/>
+      <c r="D199" s="6" t="n">
+        <v>3.5435</v>
+      </c>
+      <c r="E199" s="2" t="n"/>
+      <c r="F199" s="2" t="n"/>
+      <c r="G199" s="5" t="n">
+        <v>5.0866</v>
+      </c>
+      <c r="H199" s="2" t="n"/>
+      <c r="I199" s="2" t="n"/>
+    </row>
+    <row r="200" ht="22" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-CPLNG — COUPLING</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>1-1/4"</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="n"/>
+      <c r="D200" s="6" t="n">
+        <v>2.318</v>
+      </c>
+      <c r="E200" s="2" t="n"/>
+      <c r="F200" s="2" t="n"/>
+      <c r="G200" s="5" t="n">
+        <v>3.3282</v>
+      </c>
+      <c r="H200" s="2" t="n"/>
+      <c r="I200" s="2" t="n"/>
+    </row>
+    <row r="201" ht="22" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-CPLNG — COUPLING</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="n"/>
+      <c r="D201" s="6" t="n">
+        <v>6.4315</v>
+      </c>
+      <c r="E201" s="2" t="n"/>
+      <c r="F201" s="2" t="n"/>
+      <c r="G201" s="5" t="n">
+        <v>9.2902</v>
+      </c>
+      <c r="H201" s="2" t="n"/>
+      <c r="I201" s="2" t="n"/>
+    </row>
+    <row r="202" ht="22" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-CPLNG — COUPLING</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>2-1/2"</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n"/>
+      <c r="D202" s="6" t="n">
+        <v>10.3455</v>
+      </c>
+      <c r="E202" s="2" t="n"/>
+      <c r="F202" s="2" t="n"/>
+      <c r="G202" s="5" t="n">
+        <v>14.9995</v>
+      </c>
+      <c r="H202" s="2" t="n"/>
+      <c r="I202" s="2" t="n"/>
+    </row>
+    <row r="203" ht="22" customHeight="1">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-CPLNG — COUPLING</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n"/>
+      <c r="D203" s="6" t="n">
+        <v>15.3689</v>
+      </c>
+      <c r="E203" s="2" t="n"/>
+      <c r="F203" s="2" t="n"/>
+      <c r="G203" s="5" t="n">
+        <v>21.9775</v>
+      </c>
+      <c r="H203" s="2" t="n"/>
+      <c r="I203" s="2" t="n"/>
+    </row>
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-CPLNG — COUPLING</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="n"/>
+      <c r="D204" s="6" t="n">
+        <v>33.1333</v>
+      </c>
+      <c r="E204" s="2" t="n"/>
+      <c r="F204" s="2" t="n"/>
+      <c r="G204" s="5" t="n">
+        <v>47.6923</v>
+      </c>
+      <c r="H204" s="2" t="n"/>
+      <c r="I204" s="2" t="n"/>
+    </row>
+    <row r="205" ht="22" customHeight="1">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SCH80 — ASTM CPVC SCH80 PIPE</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>1"</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n"/>
+      <c r="D205" s="3" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="E205" s="2" t="n"/>
+      <c r="F205" s="2" t="n"/>
+      <c r="G205" s="5" t="n">
+        <v>1.3437</v>
+      </c>
+      <c r="H205" s="2" t="n"/>
+      <c r="I205" s="5" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="206" ht="22" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SCH80 — ASTM CPVC SCH80 PIPE</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="n"/>
+      <c r="D206" s="3" t="n">
+        <v>0.6516</v>
+      </c>
+      <c r="E206" s="2" t="n"/>
+      <c r="F206" s="2" t="n"/>
+      <c r="G206" s="5" t="n">
+        <v>2.2489</v>
+      </c>
+      <c r="H206" s="2" t="n"/>
+      <c r="I206" s="5" t="n">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="207" ht="22" customHeight="1">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SCH80 — ASTM CPVC SCH80 PIPE</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>1-1/4"</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="n"/>
+      <c r="D207" s="3" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="E207" s="2" t="n"/>
+      <c r="F207" s="2" t="n"/>
+      <c r="G207" s="5" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="H207" s="2" t="n"/>
+      <c r="I207" s="5" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="1">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SCH80 — ASTM CPVC SCH80 PIPE</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>1/2"</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="n"/>
+      <c r="D208" s="3" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="E208" s="2" t="n"/>
+      <c r="F208" s="2" t="n"/>
+      <c r="G208" s="5" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="H208" s="2" t="n"/>
+      <c r="I208" s="5" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="209" ht="22" customHeight="1">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SCH80 — ASTM CPVC SCH80 PIPE</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="n"/>
+      <c r="D209" s="6" t="n">
+        <v>1.4159</v>
+      </c>
+      <c r="E209" s="2" t="n"/>
+      <c r="F209" s="2" t="n"/>
+      <c r="G209" s="5" t="n">
+        <v>4.8867</v>
+      </c>
+      <c r="H209" s="2" t="n"/>
+      <c r="I209" s="5" t="n">
+        <v>5.66</v>
+      </c>
+    </row>
+    <row r="210" ht="22" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SCH80 — ASTM CPVC SCH80 PIPE</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>2-1/2"</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="n"/>
+      <c r="D210" s="6" t="n">
+        <v>1.3753</v>
+      </c>
+      <c r="E210" s="2" t="n"/>
+      <c r="F210" s="2" t="n"/>
+      <c r="G210" s="5" t="n">
+        <v>4.7464</v>
+      </c>
+      <c r="H210" s="2" t="n"/>
+      <c r="I210" s="5" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="211" ht="22" customHeight="1">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SCH80 — ASTM CPVC SCH80 PIPE</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="n"/>
+      <c r="D211" s="6" t="n">
+        <v>2.7843</v>
+      </c>
+      <c r="E211" s="2" t="n"/>
+      <c r="F211" s="2" t="n"/>
+      <c r="G211" s="5" t="n">
+        <v>9.6092</v>
+      </c>
+      <c r="H211" s="2" t="n"/>
+      <c r="I211" s="5" t="n">
+        <v>11.14</v>
+      </c>
+    </row>
+    <row r="212" ht="22" customHeight="1">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SCH80 — ASTM CPVC SCH80 PIPE</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>3/4"</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="n"/>
+      <c r="D212" s="3" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="E212" s="2" t="n"/>
+      <c r="F212" s="2" t="n"/>
+      <c r="G212" s="5" t="n">
+        <v>1.4492</v>
+      </c>
+      <c r="H212" s="2" t="n"/>
+      <c r="I212" s="5" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="213" ht="22" customHeight="1">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SCH80 — ASTM CPVC SCH80 PIPE</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="n"/>
+      <c r="D213" s="6" t="n">
+        <v>4.0239</v>
+      </c>
+      <c r="E213" s="2" t="n"/>
+      <c r="F213" s="2" t="n"/>
+      <c r="G213" s="5" t="n">
+        <v>13.8875</v>
+      </c>
+      <c r="H213" s="2" t="n"/>
+      <c r="I213" s="5" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="214" ht="22" customHeight="1">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR11 — CPVC ASTM 2846 PIPE SDR-11</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>1" x 2.6"</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="n"/>
+      <c r="D214" s="3" t="n">
+        <v>0.9898</v>
+      </c>
+      <c r="E214" s="2" t="n"/>
+      <c r="F214" s="2" t="n"/>
+      <c r="G214" s="5" t="n">
+        <v>1.4582</v>
+      </c>
+      <c r="H214" s="2" t="n"/>
+      <c r="I214" s="5" t="n">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="215" ht="22" customHeight="1">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR11 — CPVC ASTM 2846 PIPE SDR-11</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>1-1/2" x 3.76"</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="n"/>
+      <c r="D215" s="6" t="n">
+        <v>2.0659</v>
+      </c>
+      <c r="E215" s="2" t="n"/>
+      <c r="F215" s="2" t="n"/>
+      <c r="G215" s="5" t="n">
+        <v>3.0435</v>
+      </c>
+      <c r="H215" s="2" t="n"/>
+      <c r="I215" s="5" t="n">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="216" ht="22" customHeight="1">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR11 — CPVC ASTM 2846 PIPE SDR-11</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>1-1/4" x 3.18"</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="n"/>
+      <c r="D216" s="6" t="n">
+        <v>1.4824</v>
+      </c>
+      <c r="E216" s="2" t="n"/>
+      <c r="F216" s="2" t="n"/>
+      <c r="G216" s="5" t="n">
+        <v>2.1833</v>
+      </c>
+      <c r="H216" s="2" t="n"/>
+      <c r="I216" s="5" t="n">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="217" ht="22" customHeight="1">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR11 — CPVC ASTM 2846 PIPE SDR-11</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>1/2" x 1.73"</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="n"/>
+      <c r="D217" s="3" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="E217" s="2" t="n"/>
+      <c r="F217" s="2" t="n"/>
+      <c r="G217" s="4" t="n">
+        <v>0.5198</v>
+      </c>
+      <c r="H217" s="2" t="n"/>
+      <c r="I217" s="5" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="218" ht="22" customHeight="1">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR11 — CPVC ASTM 2846 PIPE SDR-11</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>2" x 4.9"</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="n"/>
+      <c r="D218" s="6" t="n">
+        <v>3.5266</v>
+      </c>
+      <c r="E218" s="2" t="n"/>
+      <c r="F218" s="2" t="n"/>
+      <c r="G218" s="5" t="n">
+        <v>5.1958</v>
+      </c>
+      <c r="H218" s="2" t="n"/>
+      <c r="I218" s="5" t="n">
+        <v>14.11</v>
+      </c>
+    </row>
+    <row r="219" ht="22" customHeight="1">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR11 — CPVC ASTM 2846 PIPE SDR-11</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>3/4" x 2.03"</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="n"/>
+      <c r="D219" s="3" t="n">
+        <v>0.5931</v>
+      </c>
+      <c r="E219" s="2" t="n"/>
+      <c r="F219" s="2" t="n"/>
+      <c r="G219" s="4" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="H219" s="2" t="n"/>
+      <c r="I219" s="5" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="220" ht="22" customHeight="1">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR13.5 — CPVC ASTM 2846 PIPE SDR-13.5</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>1" x 2.03"</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="n"/>
+      <c r="D220" s="3" t="n">
+        <v>0.7893</v>
+      </c>
+      <c r="E220" s="2" t="n"/>
+      <c r="F220" s="2" t="n"/>
+      <c r="G220" s="5" t="n">
+        <v>1.1763</v>
+      </c>
+      <c r="H220" s="2" t="n"/>
+      <c r="I220" s="5" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="221" ht="22" customHeight="1">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR13.5 — CPVC ASTM 2846 PIPE SDR-13.5</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>1-1/2" x 3.06"</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="n"/>
+      <c r="D221" s="6" t="n">
+        <v>1.7118</v>
+      </c>
+      <c r="E221" s="2" t="n"/>
+      <c r="F221" s="2" t="n"/>
+      <c r="G221" s="5" t="n">
+        <v>2.5456</v>
+      </c>
+      <c r="H221" s="2" t="n"/>
+      <c r="I221" s="5" t="n">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="222" ht="22" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR13.5 — CPVC ASTM 2846 PIPE SDR-13.5</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>1-1/4" x 2.59"</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n"/>
+      <c r="D222" s="6" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="E222" s="2" t="n"/>
+      <c r="F222" s="2" t="n"/>
+      <c r="G222" s="5" t="n">
+        <v>1.8116</v>
+      </c>
+      <c r="H222" s="2" t="n"/>
+      <c r="I222" s="5" t="n">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="223" ht="22" customHeight="1">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR13.5 — CPVC ASTM 2846 PIPE SDR-13.5</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>1/2" x 1.51"</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="n"/>
+      <c r="D223" s="3" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="E223" s="2" t="n"/>
+      <c r="F223" s="2" t="n"/>
+      <c r="G223" s="4" t="n">
+        <v>0.4667</v>
+      </c>
+      <c r="H223" s="2" t="n"/>
+      <c r="I223" s="5" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="224" ht="22" customHeight="1">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR13.5 — CPVC ASTM 2846 PIPE SDR-13.5</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>2" x 4.0"</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="n"/>
+      <c r="D224" s="6" t="n">
+        <v>2.9291</v>
+      </c>
+      <c r="E224" s="2" t="n"/>
+      <c r="F224" s="2" t="n"/>
+      <c r="G224" s="5" t="n">
+        <v>4.3557</v>
+      </c>
+      <c r="H224" s="2" t="n"/>
+      <c r="I224" s="5" t="n">
+        <v>11.72</v>
+      </c>
+    </row>
+    <row r="225" ht="22" customHeight="1">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-PIPE-SDR13.5 — CPVC ASTM 2846 PIPE SDR-13.5</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>3/4" x 1.73"</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="n"/>
+      <c r="D225" s="3" t="n">
+        <v>0.5171</v>
+      </c>
+      <c r="E225" s="2" t="n"/>
+      <c r="F225" s="2" t="n"/>
+      <c r="G225" s="4" t="n">
+        <v>0.7671</v>
+      </c>
+      <c r="H225" s="2" t="n"/>
+      <c r="I225" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="226" ht="22" customHeight="1">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-TEE — TEE</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>1"</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="n"/>
+      <c r="D226" s="6" t="n">
+        <v>4.5037</v>
+      </c>
+      <c r="E226" s="2" t="n"/>
+      <c r="F226" s="2" t="n"/>
+      <c r="G226" s="5" t="n">
+        <v>6.4496</v>
+      </c>
+      <c r="H226" s="2" t="n"/>
+      <c r="I226" s="2" t="n"/>
+    </row>
+    <row r="227" ht="22" customHeight="1">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-TEE — TEE</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>1-1/2"</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="n"/>
+      <c r="D227" s="6" t="n">
+        <v>10.2319</v>
+      </c>
+      <c r="E227" s="2" t="n"/>
+      <c r="F227" s="2" t="n"/>
+      <c r="G227" s="5" t="n">
+        <v>14.6851</v>
+      </c>
+      <c r="H227" s="2" t="n"/>
+      <c r="I227" s="2" t="n"/>
+    </row>
+    <row r="228" ht="22" customHeight="1">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-TEE — TEE</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>1/2"</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="n"/>
+      <c r="D228" s="6" t="n">
+        <v>1.1685</v>
+      </c>
+      <c r="E228" s="2" t="n"/>
+      <c r="F228" s="2" t="n"/>
+      <c r="G228" s="5" t="n">
+        <v>1.6802</v>
+      </c>
+      <c r="H228" s="2" t="n"/>
+      <c r="I228" s="2" t="n"/>
+    </row>
+    <row r="229" ht="22" customHeight="1">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-TEE — TEE</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="n"/>
+      <c r="D229" s="6" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="E229" s="2" t="n"/>
+      <c r="F229" s="2" t="n"/>
+      <c r="G229" s="5" t="n">
+        <v>25.4443</v>
+      </c>
+      <c r="H229" s="2" t="n"/>
+      <c r="I229" s="2" t="n"/>
+    </row>
+    <row r="230" ht="22" customHeight="1">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-TEE — TEE</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>3/4"</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="n"/>
+      <c r="D230" s="6" t="n">
+        <v>2.5365</v>
+      </c>
+      <c r="E230" s="2" t="n"/>
+      <c r="F230" s="2" t="n"/>
+      <c r="G230" s="5" t="n">
+        <v>3.6526</v>
+      </c>
+      <c r="H230" s="2" t="n"/>
+      <c r="I230" s="2" t="n"/>
+    </row>
+    <row r="231" ht="22" customHeight="1">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>CPVC-TEE — TEE</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="n"/>
+      <c r="D231" s="6" t="n">
+        <v>95.949</v>
+      </c>
+      <c r="E231" s="2" t="n"/>
+      <c r="F231" s="2" t="n"/>
+      <c r="G231" s="5" t="n">
+        <v>138.2361</v>
+      </c>
+      <c r="H231" s="2" t="n"/>
+      <c r="I231" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I182"/>
+  <autoFilter ref="A1:I231"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5121,21 +6286,21 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Nine columns: APBS item, Size, Palconn/Tommur/Zhenpeng FOB, Palconn/Tommur/Zhenpeng DDP or est landed, APBS selling price.</t>
+          <t>One list: every priced quote we have from Palconn, Tommur, and Zhenpeng. Blank = that mill did not quote a number. You decide what to order.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Blank = that mill did not quote this SKU (or no site price).</t>
+          <t>PEX pipe and fittings on this sheet are 1/2", 3/4", and 1" only. 1-1/4 / 1-1/2 / 2" PEX is off the list.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Green = lowest FOB among mills that quoted that row. Landed is not highlighted: Tommur DDP is mill DDP (often near FOB); Palconn/Zhenpeng are US est landed (FOB × 1.43 + $10k ocean).</t>
+          <t>Green = lowest FOB among mills that quoted that row.</t>
         </is>
       </c>
     </row>
@@ -5145,42 +6310,42 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Palconn FOB = 10 Sep sheet; 8 Sep FOB kept on DWV she dropped off the 10 Sep return.</t>
+          <t>Palconn FOB = 10 Sep sheet; 8 Sep FOB kept on DWV she dropped off the 10 Sep return. Palconn est landed = FOB × 1.43 + $10,000 / 67.7 CBM × CBM per selling unit (ocean $0 when she did not give CBM).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Palconn est landed = FOB × 1.43 + $10,000 / 67.7 CBM × CBM per selling unit.</t>
+          <t>Tommur FOB = yellow FOB from Tommur_Cost_Margin_Tracker + Factory_Order_PVC_PEX_45HQ. Tommur landed = mill DDP if present, else Est_Landed_45HQ, else FOB × 1.43.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Tommur FOB = Factory_Order_PVC_PEX_45HQ yellow FOB. Tommur landed = mill DDP if present, else Est_Landed_45HQ ($10k/45HQ).</t>
+          <t>Palconn PVC pipe is a 20 ft stick. Tommur PVC/CPVC pipe in the book is $/ft — on Palconn stick rows Tommur FOB and DDP/landed are ×20 so the cells sit next to Palconn. Tommur-only pipe sizes stay $/ft.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Zhenpeng FOB = 5 Sep 2026 REV PI. Est landed = FOB × 1.43 + $10,000 × 2.3 CBM / 86 CBM / 55,100 pcs (pallet on a 45'HQ).</t>
+          <t>Zhenpeng FOB = 5 Sep 2026 REV PI (10 SKUs). Est landed = FOB × 1.43 + $10,000 × 2.3 CBM / 86 CBM / 55,100 pcs. Plugs / extra tees were never on the REV PI — left blank.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>APBS selling price = assets/products.csv Price. PVC 1½" solid on the site looks $/ft; Palconn/Tommur pipe rows are 20 ft sticks.</t>
+          <t>APBS selling price = assets/products.csv. Blank = not on the site. PVC 1-1/2" solid on the site looks $/ft; 2" / 3" / 4" look like stick prices.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>PEX 1¼ / 1½ / 2" stay on Tommur rows for the record — do not restock. Palconn and Zhenpeng are ½ / ¾ / 1" only.</t>
+          <t>1" F2159 female adapter: Palconn returned // — no number to fill.</t>
         </is>
       </c>
     </row>
